--- a/web/files/九龙-西南九龙-维港汇 III.xlsx
+++ b/web/files/九龙-西南九龙-维港汇 III.xlsx
@@ -766,7 +766,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>2021-04-29</t>
+          <t>2021-04-30</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
@@ -828,7 +828,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2021-04-29</t>
+          <t>2021-04-30</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
@@ -890,7 +890,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-11-11</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -952,7 +952,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-25</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2024-03-28</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2024-12-29</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2024-11-26</t>
+          <t>2024-11-27</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2024-04-07</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2024-04-28</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2023-11-28</t>
+          <t>2023-11-29</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-11-11</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2023-12-05</t>
+          <t>2023-12-06</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -2874,7 +2874,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2024-01-11</t>
+          <t>2024-01-12</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -2998,7 +2998,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2023-12-17</t>
+          <t>2023-12-18</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -3246,7 +3246,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -3308,7 +3308,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-05</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2024-04-07</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -3742,7 +3742,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2024-11-27</t>
+          <t>2024-11-28</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-04-11</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -3990,7 +3990,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2024-12-15</t>
+          <t>2024-12-16</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -4052,7 +4052,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2025-01-27</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -4114,7 +4114,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -4176,7 +4176,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -4238,7 +4238,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -4300,7 +4300,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -4610,7 +4610,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -4672,7 +4672,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -4734,7 +4734,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -4796,7 +4796,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -4858,7 +4858,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -4920,7 +4920,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -4982,7 +4982,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -5044,7 +5044,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2022-02-24</t>
+          <t>2022-02-25</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -5168,7 +5168,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -5230,7 +5230,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -5292,7 +5292,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -5354,7 +5354,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -5416,7 +5416,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2022-01-28</t>
+          <t>2022-01-29</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -5478,7 +5478,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2023-10-05</t>
+          <t>2023-10-06</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -5602,7 +5602,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -5726,7 +5726,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -5788,7 +5788,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -5850,7 +5850,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2021-11-04</t>
+          <t>2021-11-05</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -5912,7 +5912,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -5974,7 +5974,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2021-10-04</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -6036,7 +6036,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2022-07-07</t>
+          <t>2022-07-08</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -6160,7 +6160,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -6346,7 +6346,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -6408,7 +6408,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2021-09-15</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -6470,7 +6470,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -6532,7 +6532,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -6842,7 +6842,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2021-04-29</t>
+          <t>2021-04-30</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -6904,7 +6904,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -6966,7 +6966,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -7028,7 +7028,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -7090,7 +7090,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -7152,7 +7152,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2021-11-01</t>
+          <t>2021-11-02</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
@@ -7214,7 +7214,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -7276,7 +7276,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2021-07-22</t>
+          <t>2021-07-23</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -7338,7 +7338,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -7400,7 +7400,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -7462,7 +7462,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -7524,7 +7524,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -7586,7 +7586,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2021-09-14</t>
+          <t>2021-09-15</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="H114" s="5" t="n">
@@ -7710,7 +7710,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="H115" s="5" t="n">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2022-04-24</t>
+          <t>2022-04-25</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
@@ -7834,7 +7834,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -7896,7 +7896,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -7958,7 +7958,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -8020,7 +8020,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2021-09-17</t>
+          <t>2021-09-18</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -8082,7 +8082,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
@@ -8144,7 +8144,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2021-09-23</t>
+          <t>2021-09-24</t>
         </is>
       </c>
       <c r="H122" s="5" t="n">
@@ -8206,7 +8206,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2024-12-29</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="H124" s="5" t="n">
@@ -8330,7 +8330,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2022-06-28</t>
+          <t>2022-06-29</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -8392,7 +8392,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="H126" s="5" t="n">
@@ -8454,7 +8454,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2021-10-07</t>
+          <t>2021-10-08</t>
         </is>
       </c>
       <c r="H127" s="5" t="n">
@@ -8516,7 +8516,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2024-01-11</t>
+          <t>2024-01-12</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
@@ -8578,7 +8578,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2021-09-23</t>
+          <t>2021-09-24</t>
         </is>
       </c>
       <c r="H129" s="5" t="n">
@@ -8640,7 +8640,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2022-01-16</t>
+          <t>2022-01-17</t>
         </is>
       </c>
       <c r="H130" s="5" t="n">
@@ -8702,7 +8702,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="H132" s="5" t="n">
@@ -8826,7 +8826,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2023-03-19</t>
+          <t>2023-03-20</t>
         </is>
       </c>
       <c r="H133" s="5" t="n">
@@ -8888,7 +8888,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
@@ -8950,7 +8950,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
@@ -9012,7 +9012,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="H136" s="5" t="n">
@@ -9074,7 +9074,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2021-11-15</t>
+          <t>2021-11-16</t>
         </is>
       </c>
       <c r="H137" s="5" t="n">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="H138" s="5" t="n">
@@ -9198,7 +9198,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2024-12-18</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="H139" s="5" t="n">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2022-02-16</t>
+          <t>2022-02-17</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
@@ -9322,7 +9322,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2021-09-28</t>
+          <t>2021-09-29</t>
         </is>
       </c>
       <c r="H141" s="5" t="n">
@@ -9384,7 +9384,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2023-07-13</t>
+          <t>2023-07-14</t>
         </is>
       </c>
       <c r="H142" s="5" t="n">
@@ -9446,7 +9446,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2021-08-12</t>
+          <t>2021-08-13</t>
         </is>
       </c>
       <c r="H143" s="5" t="n">
@@ -9508,7 +9508,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="H144" s="5" t="n">
@@ -9570,7 +9570,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="H145" s="5" t="n">
@@ -9632,7 +9632,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="H146" s="5" t="n">
@@ -9694,7 +9694,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2021-11-29</t>
+          <t>2021-11-30</t>
         </is>
       </c>
       <c r="H147" s="5" t="n">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="H148" s="5" t="n">
@@ -9818,7 +9818,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>2021-11-17</t>
+          <t>2021-11-18</t>
         </is>
       </c>
       <c r="H149" s="5" t="n">
@@ -9880,7 +9880,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2021-08-03</t>
+          <t>2021-08-04</t>
         </is>
       </c>
       <c r="H150" s="5" t="n">
@@ -9942,7 +9942,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2021-09-26</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="H151" s="5" t="n">
@@ -10004,7 +10004,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2025-01-14</t>
         </is>
       </c>
       <c r="H152" s="5" t="n">
@@ -10066,7 +10066,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2022-05-16</t>
+          <t>2022-05-17</t>
         </is>
       </c>
       <c r="H153" s="5" t="n">
@@ -10128,7 +10128,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>2022-01-13</t>
+          <t>2022-01-14</t>
         </is>
       </c>
       <c r="H154" s="5" t="n">
@@ -10190,7 +10190,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2021-08-11</t>
+          <t>2021-08-12</t>
         </is>
       </c>
       <c r="H155" s="5" t="n">
@@ -10252,7 +10252,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2022-05-05</t>
+          <t>2022-05-06</t>
         </is>
       </c>
       <c r="H156" s="5" t="n">
@@ -10314,7 +10314,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2021-08-01</t>
+          <t>2021-08-02</t>
         </is>
       </c>
       <c r="H157" s="5" t="n">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="H158" s="5" t="n">
@@ -10438,7 +10438,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2024-12-02</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="H159" s="5" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2021-11-14</t>
+          <t>2021-11-15</t>
         </is>
       </c>
       <c r="H160" s="5" t="n">
@@ -10562,7 +10562,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2021-11-09</t>
+          <t>2021-11-10</t>
         </is>
       </c>
       <c r="H161" s="5" t="n">
@@ -10624,7 +10624,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2021-04-22</t>
+          <t>2021-04-23</t>
         </is>
       </c>
       <c r="H162" s="5" t="n">
@@ -10686,7 +10686,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2021-11-10</t>
+          <t>2021-11-11</t>
         </is>
       </c>
       <c r="H163" s="5" t="n">
@@ -10748,7 +10748,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2021-04-27</t>
+          <t>2021-04-28</t>
         </is>
       </c>
       <c r="H164" s="5" t="n">
@@ -10810,7 +10810,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2021-09-14</t>
+          <t>2021-09-15</t>
         </is>
       </c>
       <c r="H165" s="5" t="n">
@@ -10872,7 +10872,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="H166" s="5" t="n">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="H167" s="5" t="n">
@@ -10996,7 +10996,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2021-11-25</t>
+          <t>2021-11-26</t>
         </is>
       </c>
       <c r="H168" s="5" t="n">
@@ -11058,7 +11058,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>2021-08-10</t>
+          <t>2021-08-11</t>
         </is>
       </c>
       <c r="H169" s="5" t="n">
@@ -11120,7 +11120,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
+          <t>2021-11-12</t>
         </is>
       </c>
       <c r="H170" s="5" t="n">
@@ -11182,7 +11182,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2021-08-08</t>
+          <t>2021-08-09</t>
         </is>
       </c>
       <c r="H171" s="5" t="n">
@@ -11244,7 +11244,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2021-09-15</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="H172" s="5" t="n">
@@ -11306,7 +11306,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="H173" s="5" t="n">
@@ -11368,7 +11368,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2021-11-18</t>
+          <t>2021-11-19</t>
         </is>
       </c>
       <c r="H174" s="5" t="n">
@@ -11430,7 +11430,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2021-11-25</t>
+          <t>2021-11-26</t>
         </is>
       </c>
       <c r="H175" s="5" t="n">
@@ -11492,7 +11492,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2021-07-01</t>
+          <t>2021-07-02</t>
         </is>
       </c>
       <c r="H176" s="5" t="n">
@@ -11554,7 +11554,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2021-10-22</t>
+          <t>2021-10-23</t>
         </is>
       </c>
       <c r="H177" s="5" t="n">
@@ -11616,7 +11616,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2021-07-07</t>
+          <t>2021-07-08</t>
         </is>
       </c>
       <c r="H178" s="5" t="n">
@@ -11678,7 +11678,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2021-09-20</t>
+          <t>2021-09-21</t>
         </is>
       </c>
       <c r="H179" s="5" t="n">
@@ -11740,7 +11740,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="H180" s="5" t="n">
@@ -11802,7 +11802,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="H181" s="5" t="n">
@@ -11864,7 +11864,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="H182" s="5" t="n">
@@ -11926,7 +11926,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2021-04-20</t>
+          <t>2021-04-21</t>
         </is>
       </c>
       <c r="H183" s="5" t="n">
@@ -11988,7 +11988,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2021-11-03</t>
+          <t>2021-11-04</t>
         </is>
       </c>
       <c r="H184" s="5" t="n">
@@ -12050,7 +12050,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2021-08-05</t>
+          <t>2021-08-06</t>
         </is>
       </c>
       <c r="H185" s="5" t="n">
@@ -12112,7 +12112,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2021-09-06</t>
+          <t>2021-09-07</t>
         </is>
       </c>
       <c r="H186" s="5" t="n">
@@ -12174,7 +12174,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H187" s="5" t="n">
@@ -12236,7 +12236,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2021-09-23</t>
+          <t>2021-09-24</t>
         </is>
       </c>
       <c r="H188" s="5" t="n">
@@ -12298,7 +12298,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2021-11-10</t>
+          <t>2021-11-11</t>
         </is>
       </c>
       <c r="H189" s="5" t="n">
@@ -12360,7 +12360,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H190" s="5" t="n">
@@ -12422,7 +12422,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2021-11-01</t>
         </is>
       </c>
       <c r="H191" s="5" t="n">
@@ -12484,7 +12484,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2021-08-04</t>
+          <t>2021-08-05</t>
         </is>
       </c>
       <c r="H192" s="5" t="n">
@@ -12546,7 +12546,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="H193" s="5" t="n">
@@ -12608,7 +12608,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="H194" s="5" t="n">
@@ -12670,7 +12670,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>2021-09-22</t>
+          <t>2021-09-23</t>
         </is>
       </c>
       <c r="H195" s="5" t="n">
@@ -12732,7 +12732,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2021-11-21</t>
+          <t>2021-11-22</t>
         </is>
       </c>
       <c r="H196" s="5" t="n">
@@ -12794,7 +12794,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H197" s="5" t="n">
@@ -12856,7 +12856,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="H198" s="5" t="n">
@@ -12918,7 +12918,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2021-04-26</t>
+          <t>2021-04-27</t>
         </is>
       </c>
       <c r="H199" s="5" t="n">
@@ -12980,7 +12980,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="H200" s="5" t="n">
@@ -13042,7 +13042,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>2024-11-24</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="H201" s="5" t="n">
@@ -13104,7 +13104,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2021-10-21</t>
+          <t>2021-10-22</t>
         </is>
       </c>
       <c r="H202" s="5" t="n">
@@ -13166,7 +13166,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="H203" s="5" t="n">
@@ -13228,7 +13228,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2021-06-28</t>
+          <t>2021-06-29</t>
         </is>
       </c>
       <c r="H204" s="5" t="n">
@@ -13290,7 +13290,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>2021-09-24</t>
+          <t>2021-09-25</t>
         </is>
       </c>
       <c r="H205" s="5" t="n">
@@ -13352,7 +13352,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>2021-05-12</t>
+          <t>2021-05-13</t>
         </is>
       </c>
       <c r="H206" s="5" t="n">
@@ -13414,7 +13414,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2021-08-19</t>
+          <t>2021-08-20</t>
         </is>
       </c>
       <c r="H207" s="5" t="n">
@@ -13476,7 +13476,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="H208" s="5" t="n">
@@ -13538,7 +13538,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>2021-09-22</t>
+          <t>2021-09-23</t>
         </is>
       </c>
       <c r="H209" s="5" t="n">
@@ -13600,7 +13600,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>2021-10-28</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="H210" s="5" t="n">
@@ -13662,7 +13662,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2021-07-08</t>
+          <t>2021-07-09</t>
         </is>
       </c>
       <c r="H211" s="5" t="n">
@@ -13724,7 +13724,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="H212" s="5" t="n">
@@ -13786,7 +13786,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2021-07-08</t>
+          <t>2021-07-09</t>
         </is>
       </c>
       <c r="H213" s="5" t="n">
@@ -13848,7 +13848,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>2021-07-23</t>
+          <t>2021-07-24</t>
         </is>
       </c>
       <c r="H214" s="5" t="n">
@@ -13910,7 +13910,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
+          <t>2023-04-24</t>
         </is>
       </c>
       <c r="H215" s="5" t="n">
@@ -13972,7 +13972,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>2021-09-14</t>
+          <t>2021-09-15</t>
         </is>
       </c>
       <c r="H216" s="5" t="n">
@@ -14034,7 +14034,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>2021-11-16</t>
+          <t>2021-11-17</t>
         </is>
       </c>
       <c r="H217" s="5" t="n">
@@ -14096,7 +14096,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>2021-07-05</t>
+          <t>2021-07-06</t>
         </is>
       </c>
       <c r="H218" s="5" t="n">
@@ -14158,7 +14158,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-10-01</t>
         </is>
       </c>
       <c r="H219" s="5" t="n">
@@ -14220,7 +14220,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>2021-04-20</t>
+          <t>2021-04-21</t>
         </is>
       </c>
       <c r="H220" s="5" t="n">
@@ -14282,7 +14282,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>2021-08-12</t>
+          <t>2021-08-13</t>
         </is>
       </c>
       <c r="H221" s="5" t="n">
@@ -14344,7 +14344,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>2024-11-27</t>
+          <t>2024-11-28</t>
         </is>
       </c>
       <c r="H222" s="5" t="n">
@@ -14406,7 +14406,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>2022-04-21</t>
+          <t>2022-04-22</t>
         </is>
       </c>
       <c r="H223" s="5" t="n">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-04-11</t>
         </is>
       </c>
       <c r="H224" s="5" t="n">
@@ -14530,7 +14530,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>2021-10-20</t>
+          <t>2021-10-21</t>
         </is>
       </c>
       <c r="H225" s="5" t="n">
@@ -14592,7 +14592,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>2021-11-08</t>
+          <t>2021-11-09</t>
         </is>
       </c>
       <c r="H226" s="5" t="n">
@@ -14654,7 +14654,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>2021-08-11</t>
+          <t>2021-08-12</t>
         </is>
       </c>
       <c r="H227" s="5" t="n">
@@ -14716,7 +14716,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2021-08-29</t>
+          <t>2021-08-30</t>
         </is>
       </c>
       <c r="H228" s="5" t="n">
@@ -14778,7 +14778,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="H229" s="5" t="n">
@@ -14840,7 +14840,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>2022-05-04</t>
+          <t>2022-05-05</t>
         </is>
       </c>
       <c r="H230" s="5" t="n">
@@ -14902,7 +14902,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="H231" s="5" t="n">
@@ -14964,7 +14964,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>2021-10-27</t>
+          <t>2021-10-28</t>
         </is>
       </c>
       <c r="H232" s="5" t="n">
@@ -15026,7 +15026,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>2021-11-09</t>
+          <t>2021-11-10</t>
         </is>
       </c>
       <c r="H233" s="5" t="n">
@@ -15088,7 +15088,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>2021-08-16</t>
+          <t>2021-08-17</t>
         </is>
       </c>
       <c r="H234" s="5" t="n">
@@ -15150,7 +15150,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>2021-09-02</t>
+          <t>2021-09-03</t>
         </is>
       </c>
       <c r="H235" s="5" t="n">
@@ -15212,7 +15212,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="H236" s="5" t="n">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>2022-05-30</t>
+          <t>2022-05-31</t>
         </is>
       </c>
       <c r="H237" s="5" t="n">
@@ -15336,7 +15336,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>2025-01-07</t>
+          <t>2025-01-08</t>
         </is>
       </c>
       <c r="H238" s="5" t="n">
@@ -15398,7 +15398,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2021-11-01</t>
         </is>
       </c>
       <c r="H239" s="5" t="n">
@@ -15460,7 +15460,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>2022-06-01</t>
+          <t>2022-06-02</t>
         </is>
       </c>
       <c r="H240" s="5" t="n">
@@ -15522,7 +15522,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>2021-09-20</t>
+          <t>2021-09-21</t>
         </is>
       </c>
       <c r="H241" s="5" t="n">
@@ -15584,7 +15584,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>2021-08-26</t>
+          <t>2021-08-27</t>
         </is>
       </c>
       <c r="H242" s="5" t="n">
@@ -15646,7 +15646,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>2024-11-24</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="H243" s="5" t="n">
@@ -15708,7 +15708,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="H244" s="5" t="n">
@@ -15770,7 +15770,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="H245" s="5" t="n">
@@ -15832,7 +15832,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="H246" s="5" t="n">
@@ -15894,7 +15894,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="H247" s="5" t="n">
@@ -15956,7 +15956,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="H248" s="5" t="n">
@@ -16018,7 +16018,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="H249" s="5" t="n">
@@ -16080,7 +16080,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="H250" s="5" t="n">
@@ -16142,7 +16142,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>2024-11-26</t>
+          <t>2024-11-27</t>
         </is>
       </c>
       <c r="H251" s="5" t="n">
@@ -16204,7 +16204,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="H252" s="5" t="n">
@@ -16266,7 +16266,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>2025-05-18</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="H253" s="5" t="n">
@@ -16328,7 +16328,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="H254" s="5" t="n">
@@ -16390,7 +16390,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="H255" s="5" t="n">
@@ -16452,7 +16452,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="H256" s="5" t="n">
@@ -16514,7 +16514,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>2023-02-22</t>
+          <t>2023-02-23</t>
         </is>
       </c>
       <c r="H257" s="5" t="n">
@@ -16576,7 +16576,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2024-12-12</t>
         </is>
       </c>
       <c r="H258" s="5" t="n">
@@ -16638,7 +16638,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>2024-03-19</t>
+          <t>2024-03-20</t>
         </is>
       </c>
       <c r="H259" s="5" t="n">
@@ -16700,7 +16700,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="H260" s="5" t="n">
@@ -16762,7 +16762,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="H261" s="5" t="n">
@@ -16824,7 +16824,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="H262" s="5" t="n">
@@ -16886,7 +16886,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="H263" s="5" t="n">
@@ -16948,7 +16948,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>2022-03-31</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="H264" s="5" t="n">
@@ -17010,7 +17010,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-25</t>
         </is>
       </c>
       <c r="H265" s="5" t="n">
@@ -17072,7 +17072,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>2024-06-03</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="H266" s="5" t="n">
@@ -17134,7 +17134,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="H267" s="5" t="n">
@@ -17196,7 +17196,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>2024-06-03</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="H268" s="5" t="n">
@@ -17258,7 +17258,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="H269" s="5" t="n">
@@ -17320,7 +17320,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="H270" s="5" t="n">
@@ -17382,7 +17382,7 @@
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="H271" s="5" t="n">
@@ -17444,7 +17444,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="H272" s="5" t="n">
@@ -17506,7 +17506,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="H273" s="5" t="n">
@@ -17568,7 +17568,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>2021-09-09</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="H274" s="5" t="n">
@@ -17630,7 +17630,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-25</t>
         </is>
       </c>
       <c r="H275" s="5" t="n">
@@ -17692,7 +17692,7 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="H276" s="5" t="n">
@@ -17754,7 +17754,7 @@
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>2024-01-07</t>
+          <t>2024-01-08</t>
         </is>
       </c>
       <c r="H277" s="5" t="n">
@@ -17816,7 +17816,7 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>2025-01-23</t>
+          <t>2025-01-24</t>
         </is>
       </c>
       <c r="H278" s="5" t="n">
@@ -17878,7 +17878,7 @@
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>2021-10-04</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="H279" s="5" t="n">
@@ -17940,7 +17940,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="H280" s="5" t="n">
@@ -18002,7 +18002,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>2024-09-29</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="H281" s="5" t="n">
@@ -18064,7 +18064,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>2021-11-09</t>
+          <t>2021-11-10</t>
         </is>
       </c>
       <c r="H282" s="5" t="n">
@@ -18126,7 +18126,7 @@
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="H283" s="5" t="n">
@@ -18188,7 +18188,7 @@
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>2021-09-12</t>
+          <t>2021-09-13</t>
         </is>
       </c>
       <c r="H284" s="5" t="n">
@@ -18250,7 +18250,7 @@
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="H285" s="5" t="n">
@@ -18312,7 +18312,7 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="H286" s="5" t="n">
@@ -18374,7 +18374,7 @@
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="H287" s="5" t="n">
@@ -18436,7 +18436,7 @@
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>2025-01-16</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="H288" s="5" t="n">
@@ -18498,7 +18498,7 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>2021-08-29</t>
+          <t>2021-08-30</t>
         </is>
       </c>
       <c r="H289" s="5" t="n">
@@ -18560,7 +18560,7 @@
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="H290" s="5" t="n">
@@ -18622,7 +18622,7 @@
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>2024-11-28</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="H291" s="5" t="n">
@@ -18684,7 +18684,7 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>2021-10-11</t>
+          <t>2021-10-12</t>
         </is>
       </c>
       <c r="H292" s="5" t="n">
@@ -18746,7 +18746,7 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-06-28</t>
         </is>
       </c>
       <c r="H293" s="5" t="n">
@@ -18808,7 +18808,7 @@
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>2021-08-10</t>
+          <t>2021-08-11</t>
         </is>
       </c>
       <c r="H294" s="5" t="n">
@@ -18870,7 +18870,7 @@
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-06-21</t>
         </is>
       </c>
       <c r="H295" s="5" t="n">
@@ -18932,7 +18932,7 @@
       </c>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="H296" s="5" t="n">
@@ -18994,7 +18994,7 @@
       </c>
       <c r="G297" s="3" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="H297" s="5" t="n">
@@ -19056,7 +19056,7 @@
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>2024-12-22</t>
+          <t>2024-12-23</t>
         </is>
       </c>
       <c r="H298" s="5" t="n">
@@ -19118,7 +19118,7 @@
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>2021-07-26</t>
+          <t>2021-07-27</t>
         </is>
       </c>
       <c r="H299" s="5" t="n">
@@ -19180,7 +19180,7 @@
       </c>
       <c r="G300" s="3" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="H300" s="5" t="n">
@@ -19242,7 +19242,7 @@
       </c>
       <c r="G301" s="3" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-05-04</t>
         </is>
       </c>
       <c r="H301" s="5" t="n">
@@ -19304,7 +19304,7 @@
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>2021-08-29</t>
+          <t>2021-08-30</t>
         </is>
       </c>
       <c r="H302" s="5" t="n">
@@ -19366,7 +19366,7 @@
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="H303" s="5" t="n">
@@ -19428,7 +19428,7 @@
       </c>
       <c r="G304" s="3" t="inlineStr">
         <is>
-          <t>2021-06-29</t>
+          <t>2021-06-30</t>
         </is>
       </c>
       <c r="H304" s="5" t="n">
@@ -19490,7 +19490,7 @@
       </c>
       <c r="G305" s="3" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="H305" s="5" t="n">
@@ -19552,7 +19552,7 @@
       </c>
       <c r="G306" s="3" t="inlineStr">
         <is>
-          <t>2024-04-28</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="H306" s="5" t="n">
@@ -19614,7 +19614,7 @@
       </c>
       <c r="G307" s="3" t="inlineStr">
         <is>
-          <t>2021-08-19</t>
+          <t>2021-08-20</t>
         </is>
       </c>
       <c r="H307" s="5" t="n">
@@ -19676,7 +19676,7 @@
       </c>
       <c r="G308" s="3" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2024-03-28</t>
         </is>
       </c>
       <c r="H308" s="5" t="n">
@@ -19738,7 +19738,7 @@
       </c>
       <c r="G309" s="3" t="inlineStr">
         <is>
-          <t>2021-07-01</t>
+          <t>2021-07-02</t>
         </is>
       </c>
       <c r="H309" s="5" t="n">
@@ -19800,7 +19800,7 @@
       </c>
       <c r="G310" s="3" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="H310" s="5" t="n">
@@ -19862,7 +19862,7 @@
       </c>
       <c r="G311" s="3" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="H311" s="5" t="n">
@@ -19924,7 +19924,7 @@
       </c>
       <c r="G312" s="3" t="inlineStr">
         <is>
-          <t>2021-07-21</t>
+          <t>2021-07-22</t>
         </is>
       </c>
       <c r="H312" s="5" t="n">
@@ -19986,7 +19986,7 @@
       </c>
       <c r="G313" s="3" t="inlineStr">
         <is>
-          <t>2021-11-20</t>
+          <t>2021-11-21</t>
         </is>
       </c>
       <c r="H313" s="5" t="n">
@@ -20048,7 +20048,7 @@
       </c>
       <c r="G314" s="3" t="inlineStr">
         <is>
-          <t>2021-07-06</t>
+          <t>2021-07-07</t>
         </is>
       </c>
       <c r="H314" s="5" t="n">
@@ -20110,7 +20110,7 @@
       </c>
       <c r="G315" s="3" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="H315" s="5" t="n">
@@ -20172,7 +20172,7 @@
       </c>
       <c r="G316" s="3" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="H316" s="5" t="n">
@@ -20234,7 +20234,7 @@
       </c>
       <c r="G317" s="3" t="inlineStr">
         <is>
-          <t>2021-07-28</t>
+          <t>2021-07-29</t>
         </is>
       </c>
       <c r="H317" s="5" t="n">
@@ -20296,7 +20296,7 @@
       </c>
       <c r="G318" s="3" t="inlineStr">
         <is>
-          <t>2023-06-11</t>
+          <t>2023-06-12</t>
         </is>
       </c>
       <c r="H318" s="5" t="n">
@@ -20358,7 +20358,7 @@
       </c>
       <c r="G319" s="3" t="inlineStr">
         <is>
-          <t>2021-07-05</t>
+          <t>2021-07-06</t>
         </is>
       </c>
       <c r="H319" s="5" t="n">
@@ -20420,7 +20420,7 @@
       </c>
       <c r="G320" s="3" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-07-17</t>
         </is>
       </c>
       <c r="H320" s="5" t="n">
@@ -20482,7 +20482,7 @@
       </c>
       <c r="G321" s="3" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="H321" s="5" t="n">
@@ -20544,7 +20544,7 @@
       </c>
       <c r="G322" s="3" t="inlineStr">
         <is>
-          <t>2021-07-19</t>
+          <t>2021-07-20</t>
         </is>
       </c>
       <c r="H322" s="5" t="n">
@@ -20606,7 +20606,7 @@
       </c>
       <c r="G323" s="3" t="inlineStr">
         <is>
-          <t>2021-11-29</t>
+          <t>2021-11-30</t>
         </is>
       </c>
       <c r="H323" s="5" t="n">
@@ -20668,7 +20668,7 @@
       </c>
       <c r="G324" s="3" t="inlineStr">
         <is>
-          <t>2021-07-05</t>
+          <t>2021-07-06</t>
         </is>
       </c>
       <c r="H324" s="5" t="n">
@@ -20730,7 +20730,7 @@
       </c>
       <c r="G325" s="3" t="inlineStr">
         <is>
-          <t>2024-06-03</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="H325" s="5" t="n">
@@ -20792,7 +20792,7 @@
       </c>
       <c r="G326" s="3" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="H326" s="5" t="n">
@@ -20854,7 +20854,7 @@
       </c>
       <c r="G327" s="3" t="inlineStr">
         <is>
-          <t>2021-07-13</t>
+          <t>2021-07-14</t>
         </is>
       </c>
       <c r="H327" s="5" t="n">
@@ -20916,7 +20916,7 @@
       </c>
       <c r="G328" s="3" t="inlineStr">
         <is>
-          <t>2021-09-28</t>
+          <t>2021-09-29</t>
         </is>
       </c>
       <c r="H328" s="5" t="n">
@@ -20978,7 +20978,7 @@
       </c>
       <c r="G329" s="3" t="inlineStr">
         <is>
-          <t>2021-04-21</t>
+          <t>2021-04-22</t>
         </is>
       </c>
       <c r="H329" s="5" t="n">
@@ -21040,7 +21040,7 @@
       </c>
       <c r="G330" s="3" t="inlineStr">
         <is>
-          <t>2024-06-03</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="H330" s="5" t="n">
@@ -21102,7 +21102,7 @@
       </c>
       <c r="G331" s="3" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="H331" s="5" t="n">
@@ -21164,7 +21164,7 @@
       </c>
       <c r="G332" s="3" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="H332" s="5" t="n">
@@ -21226,7 +21226,7 @@
       </c>
       <c r="G333" s="3" t="inlineStr">
         <is>
-          <t>2021-10-22</t>
+          <t>2021-10-23</t>
         </is>
       </c>
       <c r="H333" s="5" t="n">
@@ -21288,7 +21288,7 @@
       </c>
       <c r="G334" s="3" t="inlineStr">
         <is>
-          <t>2021-05-13</t>
+          <t>2021-05-14</t>
         </is>
       </c>
       <c r="H334" s="5" t="n">
@@ -21350,7 +21350,7 @@
       </c>
       <c r="G335" s="3" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="H335" s="5" t="n">
@@ -21412,7 +21412,7 @@
       </c>
       <c r="G336" s="3" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="H336" s="5" t="n">
@@ -21474,7 +21474,7 @@
       </c>
       <c r="G337" s="3" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="H337" s="5" t="n">
@@ -21536,7 +21536,7 @@
       </c>
       <c r="G338" s="3" t="inlineStr">
         <is>
-          <t>2021-06-30</t>
+          <t>2021-07-01</t>
         </is>
       </c>
       <c r="H338" s="5" t="n">
@@ -21598,7 +21598,7 @@
       </c>
       <c r="G339" s="3" t="inlineStr">
         <is>
-          <t>2021-05-23</t>
+          <t>2021-05-24</t>
         </is>
       </c>
       <c r="H339" s="5" t="n">
@@ -21660,7 +21660,7 @@
       </c>
       <c r="G340" s="3" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="H340" s="5" t="n">
@@ -21722,7 +21722,7 @@
       </c>
       <c r="G341" s="3" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="H341" s="5" t="n">
@@ -21784,7 +21784,7 @@
       </c>
       <c r="G342" s="3" t="inlineStr">
         <is>
-          <t>2021-07-14</t>
+          <t>2021-07-15</t>
         </is>
       </c>
       <c r="H342" s="5" t="n">
@@ -21846,7 +21846,7 @@
       </c>
       <c r="G343" s="3" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="H343" s="5" t="n">
@@ -21908,7 +21908,7 @@
       </c>
       <c r="G344" s="3" t="inlineStr">
         <is>
-          <t>2021-05-02</t>
+          <t>2021-05-03</t>
         </is>
       </c>
       <c r="H344" s="5" t="n">
@@ -21970,7 +21970,7 @@
       </c>
       <c r="G345" s="3" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2024-06-07</t>
         </is>
       </c>
       <c r="H345" s="5" t="n">
@@ -22032,7 +22032,7 @@
       </c>
       <c r="G346" s="3" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="H346" s="5" t="n">
@@ -22094,7 +22094,7 @@
       </c>
       <c r="G347" s="3" t="inlineStr">
         <is>
-          <t>2021-07-08</t>
+          <t>2021-07-09</t>
         </is>
       </c>
       <c r="H347" s="5" t="n">
@@ -22156,7 +22156,7 @@
       </c>
       <c r="G348" s="3" t="inlineStr">
         <is>
-          <t>2021-07-27</t>
+          <t>2021-07-28</t>
         </is>
       </c>
       <c r="H348" s="5" t="n">
@@ -22218,7 +22218,7 @@
       </c>
       <c r="G349" s="3" t="inlineStr">
         <is>
-          <t>2021-05-24</t>
+          <t>2021-05-25</t>
         </is>
       </c>
       <c r="H349" s="5" t="n">
@@ -22280,7 +22280,7 @@
       </c>
       <c r="G350" s="3" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-09-11</t>
         </is>
       </c>
       <c r="H350" s="5" t="n">
@@ -22342,7 +22342,7 @@
       </c>
       <c r="G351" s="3" t="inlineStr">
         <is>
-          <t>2024-04-28</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="H351" s="5" t="n">
@@ -22404,7 +22404,7 @@
       </c>
       <c r="G352" s="3" t="inlineStr">
         <is>
-          <t>2021-06-29</t>
+          <t>2021-06-30</t>
         </is>
       </c>
       <c r="H352" s="5" t="n">
@@ -22466,7 +22466,7 @@
       </c>
       <c r="G353" s="3" t="inlineStr">
         <is>
-          <t>2021-08-03</t>
+          <t>2021-08-04</t>
         </is>
       </c>
       <c r="H353" s="5" t="n">
@@ -22528,7 +22528,7 @@
       </c>
       <c r="G354" s="3" t="inlineStr">
         <is>
-          <t>2021-06-02</t>
+          <t>2021-06-03</t>
         </is>
       </c>
       <c r="H354" s="5" t="n">
@@ -22590,7 +22590,7 @@
       </c>
       <c r="G355" s="3" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2024-06-07</t>
         </is>
       </c>
       <c r="H355" s="5" t="n">
@@ -22652,7 +22652,7 @@
       </c>
       <c r="G356" s="3" t="inlineStr">
         <is>
-          <t>2024-05-05</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="H356" s="5" t="n">
@@ -22714,7 +22714,7 @@
       </c>
       <c r="G357" s="3" t="inlineStr">
         <is>
-          <t>2021-07-13</t>
+          <t>2021-07-14</t>
         </is>
       </c>
       <c r="H357" s="5" t="n">
@@ -22776,7 +22776,7 @@
       </c>
       <c r="G358" s="3" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="H358" s="5" t="n">
@@ -22838,7 +22838,7 @@
       </c>
       <c r="G359" s="3" t="inlineStr">
         <is>
-          <t>2021-05-16</t>
+          <t>2021-05-17</t>
         </is>
       </c>
       <c r="H359" s="5" t="n">
@@ -22900,7 +22900,7 @@
       </c>
       <c r="G360" s="3" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="H360" s="5" t="n">
@@ -22962,7 +22962,7 @@
       </c>
       <c r="G361" s="3" t="inlineStr">
         <is>
-          <t>2024-05-05</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="H361" s="5" t="n">
@@ -23024,7 +23024,7 @@
       </c>
       <c r="G362" s="3" t="inlineStr">
         <is>
-          <t>2021-07-26</t>
+          <t>2021-07-27</t>
         </is>
       </c>
       <c r="H362" s="5" t="n">
@@ -23086,7 +23086,7 @@
       </c>
       <c r="G363" s="3" t="inlineStr">
         <is>
-          <t>2021-07-24</t>
+          <t>2021-07-25</t>
         </is>
       </c>
       <c r="H363" s="5" t="n">
@@ -23148,7 +23148,7 @@
       </c>
       <c r="G364" s="3" t="inlineStr">
         <is>
-          <t>2021-04-03</t>
+          <t>2021-04-04</t>
         </is>
       </c>
       <c r="H364" s="5" t="n">
@@ -23210,7 +23210,7 @@
       </c>
       <c r="G365" s="3" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="H365" s="5" t="n">
@@ -23272,7 +23272,7 @@
       </c>
       <c r="G366" s="3" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="H366" s="5" t="n">
@@ -23334,7 +23334,7 @@
       </c>
       <c r="G367" s="3" t="inlineStr">
         <is>
-          <t>2021-07-25</t>
+          <t>2021-07-26</t>
         </is>
       </c>
       <c r="H367" s="5" t="n">
@@ -23396,7 +23396,7 @@
       </c>
       <c r="G368" s="3" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="H368" s="5" t="n">
@@ -23458,7 +23458,7 @@
       </c>
       <c r="G369" s="3" t="inlineStr">
         <is>
-          <t>2021-04-26</t>
+          <t>2021-04-27</t>
         </is>
       </c>
       <c r="H369" s="5" t="n">
@@ -23520,7 +23520,7 @@
       </c>
       <c r="G370" s="3" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="H370" s="5" t="n">
@@ -23582,7 +23582,7 @@
       </c>
       <c r="G371" s="3" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="H371" s="5" t="n">
@@ -23644,7 +23644,7 @@
       </c>
       <c r="G372" s="3" t="inlineStr">
         <is>
-          <t>2021-07-18</t>
+          <t>2021-07-19</t>
         </is>
       </c>
       <c r="H372" s="5" t="n">
@@ -23706,7 +23706,7 @@
       </c>
       <c r="G373" s="3" t="inlineStr">
         <is>
-          <t>2021-08-31</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="H373" s="5" t="n">
@@ -23768,7 +23768,7 @@
       </c>
       <c r="G374" s="3" t="inlineStr">
         <is>
-          <t>2021-06-29</t>
+          <t>2021-06-30</t>
         </is>
       </c>
       <c r="H374" s="5" t="n">
@@ -23830,7 +23830,7 @@
       </c>
       <c r="G375" s="3" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="H375" s="5" t="n">
@@ -23892,7 +23892,7 @@
       </c>
       <c r="G376" s="3" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="H376" s="5" t="n">
@@ -23954,7 +23954,7 @@
       </c>
       <c r="G377" s="3" t="inlineStr">
         <is>
-          <t>2021-07-28</t>
+          <t>2021-07-29</t>
         </is>
       </c>
       <c r="H377" s="5" t="n">
@@ -24016,7 +24016,7 @@
       </c>
       <c r="G378" s="3" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="H378" s="5" t="n">
@@ -24078,7 +24078,7 @@
       </c>
       <c r="G379" s="3" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="H379" s="5" t="n">
@@ -24140,7 +24140,7 @@
       </c>
       <c r="G380" s="3" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="H380" s="5" t="n">
@@ -24202,7 +24202,7 @@
       </c>
       <c r="G381" s="3" t="inlineStr">
         <is>
-          <t>2024-11-27</t>
+          <t>2024-11-28</t>
         </is>
       </c>
       <c r="H381" s="5" t="n">
@@ -24264,7 +24264,7 @@
       </c>
       <c r="G382" s="3" t="inlineStr">
         <is>
-          <t>2021-08-02</t>
+          <t>2021-08-03</t>
         </is>
       </c>
       <c r="H382" s="5" t="n">
@@ -24326,7 +24326,7 @@
       </c>
       <c r="G383" s="3" t="inlineStr">
         <is>
-          <t>2023-06-15</t>
+          <t>2023-06-16</t>
         </is>
       </c>
       <c r="H383" s="5" t="n">
@@ -24388,7 +24388,7 @@
       </c>
       <c r="G384" s="3" t="inlineStr">
         <is>
-          <t>2021-07-14</t>
+          <t>2021-07-15</t>
         </is>
       </c>
       <c r="H384" s="5" t="n">
@@ -24450,7 +24450,7 @@
       </c>
       <c r="G385" s="3" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="H385" s="5" t="n">
@@ -24512,7 +24512,7 @@
       </c>
       <c r="G386" s="3" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="H386" s="5" t="n">
@@ -24574,7 +24574,7 @@
       </c>
       <c r="G387" s="3" t="inlineStr">
         <is>
-          <t>2024-12-02</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="H387" s="5" t="n">
@@ -24636,7 +24636,7 @@
       </c>
       <c r="G388" s="3" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="H388" s="5" t="n">
@@ -24698,7 +24698,7 @@
       </c>
       <c r="G389" s="3" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="H389" s="5" t="n">
@@ -24760,7 +24760,7 @@
       </c>
       <c r="G390" s="3" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="H390" s="5" t="n">
@@ -24913,7 +24913,7 @@
           <t>A | 1611呎 (4+房)
 $7007万
 $43,498/呎
-(21年-04月-29日)</t>
+(21年-04月-30日)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
@@ -24921,7 +24921,7 @@
           <t>B | 1408呎 (4+房)
 $6633万
 $47,109/呎
-(21年-04月-29日)</t>
+(21年-04月-30日)</t>
         </is>
       </c>
     </row>
@@ -24936,7 +24936,7 @@
           <t>A | 920呎 (3房)
 $3088万
 $33,565/呎
-(25年-07月-13日)</t>
+(25年-07月-14日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -24944,7 +24944,7 @@
           <t>B | 929呎 (3房)
 $3098万
 $33,348/呎
-(24年-11月-10日)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
     </row>
@@ -24959,7 +24959,7 @@
           <t>A | 920呎 (3房)
 $3080万
 $33,478/呎
-(24年-04月-17日)</t>
+(24年-04月-18日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -24967,7 +24967,7 @@
           <t>B | 929呎 (3房)
 $3078万
 $33,132/呎
-(25年-07月-17日)</t>
+(25年-07月-18日)</t>
         </is>
       </c>
     </row>
@@ -24982,7 +24982,7 @@
           <t>A | 920呎 (3房)
 $3150万
 $34,239/呎
-(24年-04月-16日)</t>
+(24年-04月-17日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -24990,7 +24990,7 @@
           <t>B | 929呎 (3房)
 $3038万
 $32,702/呎
-(25年-04月-23日)</t>
+(25年-04月-24日)</t>
         </is>
       </c>
     </row>
@@ -25005,7 +25005,7 @@
           <t>A | 920呎 (3房)
 $3028万
 $32,913/呎
-(24年-04月-23日)</t>
+(24年-04月-24日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -25013,7 +25013,7 @@
           <t>B | 929呎 (3房)
 $3080万
 $33,154/呎
-(24年-08月-04日)</t>
+(24年-08月-05日)</t>
         </is>
       </c>
     </row>
@@ -25028,7 +25028,7 @@
           <t>A | 920呎 (3房)
 $3200万
 $34,783/呎
-(24年-09月-18日)</t>
+(24年-09月-19日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -25036,7 +25036,7 @@
           <t>B | 929呎 (3房)
 $3072万
 $33,068/呎
-(24年-08月-04日)</t>
+(24年-08月-05日)</t>
         </is>
       </c>
     </row>
@@ -25051,7 +25051,7 @@
           <t>A | 920呎 (3房)
 $2988万
 $32,478/呎
-(24年-03月-27日)</t>
+(24年-03月-28日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -25059,7 +25059,7 @@
           <t>B | 929呎 (3房)
 $3018万
 $32,487/呎
-(24年-10月-24日)</t>
+(24年-10月-25日)</t>
         </is>
       </c>
     </row>
@@ -25074,7 +25074,7 @@
           <t>A | 920呎 (3房)
 $2983万
 $32,424/呎
-(24年-04月-15日)</t>
+(24年-04月-16日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -25082,7 +25082,7 @@
           <t>B | 929呎 (3房)
 $2998万
 $32,271/呎
-(24年-12月-29日)</t>
+(24年-12月-30日)</t>
         </is>
       </c>
     </row>
@@ -25097,7 +25097,7 @@
           <t>A | 977呎 (3房)
 $2978万
 $30,481/呎
-(24年-04月-17日)</t>
+(24年-04月-18日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -25105,7 +25105,7 @@
           <t>B | 929呎 (3房)
 $2988万
 $32,164/呎
-(24年-11月-21日)</t>
+(24年-11月-22日)</t>
         </is>
       </c>
     </row>
@@ -25120,7 +25120,7 @@
           <t>A | 920呎 (3房)
 $2973万
 $32,315/呎
-(24年-04月-17日)</t>
+(24年-04月-18日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -25128,7 +25128,7 @@
           <t>B | 929呎 (3房)
 $3008万
 $32,379/呎
-(24年-11月-26日)</t>
+(24年-11月-27日)</t>
         </is>
       </c>
     </row>
@@ -25143,7 +25143,7 @@
           <t>A | 920呎 (3房)
 $2968万
 $32,261/呎
-(24年-04月-07日)</t>
+(24年-04月-08日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -25151,7 +25151,7 @@
           <t>B | 929呎 (3房)
 $2919万
 $31,421/呎
-(25年-04月-01日)</t>
+(25年-04月-02日)</t>
         </is>
       </c>
     </row>
@@ -25166,7 +25166,7 @@
           <t>A | 920呎 (3房)
 $2958万
 $32,152/呎
-(24年-04月-15日)</t>
+(24年-04月-16日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -25174,7 +25174,7 @@
           <t>B | 929呎 (3房)
 $3000万
 $32,293/呎
-(24年-05月-27日)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
     </row>
@@ -25189,7 +25189,7 @@
           <t>A | 920呎 (3房)
 $3000万
 $32,609/呎
-(24年-08月-08日)</t>
+(24年-08月-09日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -25197,7 +25197,7 @@
           <t>B | 929呎 (3房)
 $2880万
 $31,001/呎
-(24年-11月-05日)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
     </row>
@@ -25212,7 +25212,7 @@
           <t>A | 977呎 (3房)
 $2928万
 $29,969/呎
-(23年-11月-28日)</t>
+(23年-11月-29日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -25220,7 +25220,7 @@
           <t>B | 929呎 (3房)
 $2938万
 $31,625/呎
-(24年-04月-28日)</t>
+(24年-04月-29日)</t>
         </is>
       </c>
     </row>
@@ -25235,7 +25235,7 @@
           <t>A | 977呎 (3房)
 $2900万
 $29,683/呎
-(24年-03月-26日)</t>
+(24年-03月-27日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -25243,7 +25243,7 @@
           <t>B | 929呎 (3房)
 $2860万
 $30,786/呎
-(24年-11月-10日)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
     </row>
@@ -25258,7 +25258,7 @@
           <t>A | 977呎 (3房)
 $2880万
 $29,478/呎
-(24年-04月-08日)</t>
+(24年-04月-09日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -25266,7 +25266,7 @@
           <t>B | 929呎 (3房)
 $2938万
 $31,625/呎
-(25年-04月-16日)</t>
+(25年-04月-17日)</t>
         </is>
       </c>
     </row>
@@ -25281,7 +25281,7 @@
           <t>A | 920呎 (3房)
 $2850万
 $30,978/呎
-(23年-12月-05日)</t>
+(23年-12月-06日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -25289,7 +25289,7 @@
           <t>B | 929呎 (3房)
 $2828万
 $30,441/呎
-(24年-07月-28日)</t>
+(24年-07月-29日)</t>
         </is>
       </c>
     </row>
@@ -25304,7 +25304,7 @@
           <t>A | 977呎 (3房)
 $2808万
 $28,741/呎
-(24年-01月-11日)</t>
+(24年-01月-12日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -25312,7 +25312,7 @@
           <t>B | 929呎 (3房)
 $2800万
 $30,140/呎
-(24年-11月-04日)</t>
+(24年-11月-05日)</t>
         </is>
       </c>
     </row>
@@ -25327,7 +25327,7 @@
           <t>A | 977呎 (3房)
 $2788万
 $28,536/呎
-(23年-12月-17日)</t>
+(23年-12月-18日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -25335,7 +25335,7 @@
           <t>B | 929呎 (3房)
 $2788万
 $30,011/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
     </row>
@@ -25350,7 +25350,7 @@
           <t>A | 920呎 (3房)
 $2848万
 $30,957/呎
-(24年-10月-30日)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -25358,7 +25358,7 @@
           <t>B | 929呎 (3房)
 $2788万
 $30,011/呎
-(24年-05月-19日)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
     </row>
@@ -25373,7 +25373,7 @@
           <t>A | 977呎 (3房)
 $2750万
 $28,147/呎
-(24年-02月-04日)</t>
+(24年-02月-05日)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -25381,7 +25381,7 @@
           <t>B | 929呎 (3房)
 $2770万
 $29,817/呎
-(24年-11月-14日)</t>
+(24年-11月-15日)</t>
         </is>
       </c>
     </row>
@@ -25396,7 +25396,7 @@
           <t>A | 920呎 (3房)
 $2722万
 $29,587/呎
-(24年-03月-26日)</t>
+(24年-03月-27日)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -25404,7 +25404,7 @@
           <t>B | 929呎 (3房)
 $2760万
 $29,709/呎
-(24年-10月-07日)</t>
+(24年-10月-08日)</t>
         </is>
       </c>
     </row>
@@ -25419,7 +25419,7 @@
           <t>A | 920呎 (3房)
 $2700万
 $29,348/呎
-(24年-03月-26日)</t>
+(24年-03月-27日)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -25427,7 +25427,7 @@
           <t>B | 929呎 (3房)
 $2750万
 $29,602/呎
-(24年-05月-07日)</t>
+(24年-05月-08日)</t>
         </is>
       </c>
     </row>
@@ -25442,7 +25442,7 @@
           <t>A | 920呎 (3房)
 $2665万
 $28,967/呎
-(24年-04月-07日)</t>
+(24年-04月-08日)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -25450,7 +25450,7 @@
           <t>B | 929呎 (3房)
 $2738万
 $29,473/呎
-(24年-08月-18日)</t>
+(24年-08月-19日)</t>
         </is>
       </c>
     </row>
@@ -25465,7 +25465,7 @@
           <t>A | 920呎 (3房)
 $2633万
 $28,620/呎
-(24年-04月-08日)</t>
+(24年-04月-09日)</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
@@ -25473,7 +25473,7 @@
           <t>B | 929呎 (3房)
 $2702万
 $29,085/呎
-(24年-11月-27日)</t>
+(24年-11月-28日)</t>
         </is>
       </c>
     </row>
@@ -25488,7 +25488,7 @@
           <t>A | 920呎 (3房)
 $2643万
 $28,728/呎
-(24年-04月-10日)</t>
+(24年-04月-11日)</t>
         </is>
       </c>
       <c r="C30" s="20" t="inlineStr">
@@ -25496,7 +25496,7 @@
           <t>B | 929呎 (3房)
 $2652万
 $28,547/呎
-(25年-03月-23日)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
     </row>
@@ -25511,7 +25511,7 @@
           <t>A | 869呎 (3房)
 $2700万
 $31,070/呎
-(25年-01月-26日)</t>
+(25年-01月-27日)</t>
         </is>
       </c>
       <c r="C31" s="20" t="inlineStr">
@@ -25519,7 +25519,7 @@
           <t>B | 893呎 (3房)
 $2945万
 $32,982/呎
-(24年-12月-15日)</t>
+(24年-12月-16日)</t>
         </is>
       </c>
     </row>
@@ -25675,7 +25675,7 @@
           <t>A | 524呎 (2房)
 $1290万
 $24,618/呎
-(25年-08月-14日)</t>
+(25年-08月-15日)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
@@ -25683,7 +25683,7 @@
           <t>B | 315呎 (1房)
 $851万
 $27,013/呎
-(25年-10月-01日)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
       <c r="D5" s="20" t="inlineStr">
@@ -25691,7 +25691,7 @@
           <t>C | 318呎 (1房)
 $865万
 $27,210/呎
-(25年-06月-23日)</t>
+(25年-06月-24日)</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr">
@@ -25699,7 +25699,7 @@
           <t>D | 330呎 (1房)
 $866万
 $26,254/呎
-(25年-11月-13日)</t>
+(25年-11月-14日)</t>
         </is>
       </c>
       <c r="F5" s="20" t="inlineStr">
@@ -25707,7 +25707,7 @@
           <t>E | 278呎 (开放式)
 $772万
 $27,782/呎
-(25年-12月-14日)</t>
+(25年-12月-15日)</t>
         </is>
       </c>
       <c r="G5" s="20" t="inlineStr">
@@ -25715,7 +25715,7 @@
           <t>F | 296呎 (开放式)
 $746万
 $25,195/呎
-(25年-11月-25日)</t>
+(25年-11月-26日)</t>
         </is>
       </c>
       <c r="H5" s="21" t="inlineStr"/>
@@ -25731,7 +25731,7 @@
           <t>A | 524呎 (2房)
 $1273万
 $24,294/呎
-(25年-07月-24日)</t>
+(25年-07月-25日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -25739,7 +25739,7 @@
           <t>B | 315呎 (1房)
 $834万
 $26,485/呎
-(25年-07月-28日)</t>
+(25年-07月-29日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -25747,7 +25747,7 @@
           <t>C | 318呎 (1房)
 $848万
 $26,675/呎
-(25年-06月-23日)</t>
+(25年-06月-24日)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -25755,7 +25755,7 @@
           <t>D | 330呎 (1房)
 $849万
 $25,738/呎
-(25年-08月-14日)</t>
+(25年-08月-15日)</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
@@ -25771,7 +25771,7 @@
           <t>F | 278呎 (开放式)
 $687万
 $24,699/呎
-(25年-09月-16日)</t>
+(25年-09月-17日)</t>
         </is>
       </c>
       <c r="H6" s="21" t="inlineStr"/>
@@ -25787,7 +25787,7 @@
           <t>A | 524呎 (2房)
 $1260万
 $24,046/呎
-(25年-07月-01日)</t>
+(25年-07月-02日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -25795,7 +25795,7 @@
           <t>B | 315呎 (1房)
 $826万
 $26,219/呎
-(25年-07月-24日)</t>
+(25年-07月-25日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -25803,7 +25803,7 @@
           <t>C | 318呎 (1房)
 $959万
 $30,157/呎
-(22年-02月-24日)</t>
+(22年-02月-25日)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -25811,7 +25811,7 @@
           <t>D | 330呎 (1房)
 $841万
 $25,483/呎
-(25年-05月-28日)</t>
+(25年-05月-29日)</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">
@@ -25819,7 +25819,7 @@
           <t>E | 278呎 (开放式)
 $750万
 $26,969/呎
-(25年-11月-11日)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
       <c r="G7" s="20" t="inlineStr">
@@ -25827,7 +25827,7 @@
           <t>F | 278呎 (开放式)
 $680万
 $24,457/呎
-(25年-11月-11日)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
       <c r="H7" s="20" t="inlineStr">
@@ -25835,7 +25835,7 @@
           <t>G | 330呎 (1房)
 $854万
 $25,891/呎
-(25年-06月-26日)</t>
+(25年-06月-27日)</t>
         </is>
       </c>
     </row>
@@ -25850,7 +25850,7 @@
           <t>A | 524呎 (2房)
 $1258万
 $24,008/呎
-(25年-04月-01日)</t>
+(25年-04月-02日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -25858,7 +25858,7 @@
           <t>B | 315呎 (1房)
 $822万
 $26,090/呎
-(25年-07月-07日)</t>
+(25年-07月-08日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -25866,7 +25866,7 @@
           <t>C | 318呎 (1房)
 $915万
 $28,765/呎
-(23年-10月-05日)</t>
+(23年-10月-06日)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -25874,7 +25874,7 @@
           <t>D | 330呎 (1房)
 $837万
 $25,357/呎
-(25年-07月-24日)</t>
+(25年-07月-25日)</t>
         </is>
       </c>
       <c r="F8" s="20" t="inlineStr">
@@ -25882,7 +25882,7 @@
           <t>E | 278呎 (开放式)
 $778万
 $27,994/呎
-(22年-01月-28日)</t>
+(22年-01月-29日)</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -25890,7 +25890,7 @@
           <t>F | 278呎 (开放式)
 $676万
 $24,332/呎
-(25年-09月-27日)</t>
+(25年-09月-28日)</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr">
@@ -25898,7 +25898,7 @@
           <t>G | 330呎 (1房)
 $850万
 $25,763/呎
-(25年-06月-26日)</t>
+(25年-06月-27日)</t>
         </is>
       </c>
     </row>
@@ -25913,7 +25913,7 @@
           <t>A | 524呎 (2房)
 $1255万
 $23,950/呎
-(25年-08月-26日)</t>
+(25年-08月-27日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -25921,7 +25921,7 @@
           <t>B | 315呎 (1房)
 $900万
 $28,558/呎
-(22年-07月-07日)</t>
+(22年-07月-08日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -25929,7 +25929,7 @@
           <t>C | 318呎 (1房)
 $910万
 $28,620/呎
-(21年-10月-04日)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -25937,7 +25937,7 @@
           <t>D | 330呎 (1房)
 $837万
 $25,357/呎
-(25年-06月-17日)</t>
+(25年-06月-18日)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -25945,7 +25945,7 @@
           <t>E | 277呎 (开放式)
 $778万
 $28,095/呎
-(21年-11月-04日)</t>
+(21年-11月-05日)</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
@@ -25953,7 +25953,7 @@
           <t>F | 278呎 (开放式)
 $676万
 $24,332/呎
-(25年-10月-07日)</t>
+(25年-10月-08日)</t>
         </is>
       </c>
       <c r="H9" s="20" t="inlineStr">
@@ -25961,7 +25961,7 @@
           <t>G | 330呎 (1房)
 $846万
 $25,638/呎
-(25年-06月-22日)</t>
+(25年-06月-23日)</t>
         </is>
       </c>
     </row>
@@ -25976,7 +25976,7 @@
           <t>A | 524呎 (2房)
 $1252万
 $23,893/呎
-(25年-06月-02日)</t>
+(25年-06月-03日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -25984,7 +25984,7 @@
           <t>B | 315呎 (1房)
 $814万
 $25,832/呎
-(25年-07月-03日)</t>
+(25年-07月-04日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -25992,7 +25992,7 @@
           <t>C | 318呎 (1房)
 $945万
 $29,708/呎
-(21年-09月-15日)</t>
+(21年-09月-16日)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -26000,7 +26000,7 @@
           <t>D | 330呎 (1房)
 $828万
 $25,104/呎
-(25年-06月-19日)</t>
+(25年-06月-20日)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -26016,7 +26016,7 @@
           <t>F | 278呎 (开放式)
 $670万
 $24,092/呎
-(25年-07月-27日)</t>
+(25年-07月-28日)</t>
         </is>
       </c>
       <c r="H10" s="20" t="inlineStr">
@@ -26024,7 +26024,7 @@
           <t>G | 330呎 (1房)
 $842万
 $25,508/呎
-(25年-06月-24日)</t>
+(25年-06月-25日)</t>
         </is>
       </c>
     </row>
@@ -26039,7 +26039,7 @@
           <t>A | 524呎 (2房)
 $1246万
 $23,779/呎
-(25年-06月-23日)</t>
+(25年-06月-24日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -26047,7 +26047,7 @@
           <t>B | 315呎 (1房)
 $810万
 $25,703/呎
-(25年-07月-07日)</t>
+(25年-07月-08日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -26055,7 +26055,7 @@
           <t>C | 317呎 (1房)
 $890万
 $28,076/呎
-(21年-04月-29日)</t>
+(21年-04月-30日)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -26063,7 +26063,7 @@
           <t>D | 330呎 (1房)
 $824万
 $24,981/呎
-(25年-06月-23日)</t>
+(25年-06月-24日)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -26079,7 +26079,7 @@
           <t>F | 278呎 (开放式)
 $666万
 $23,973/呎
-(25年-07月-02日)</t>
+(25年-07月-03日)</t>
         </is>
       </c>
       <c r="H11" s="20" t="inlineStr">
@@ -26087,7 +26087,7 @@
           <t>G | 330呎 (1房)
 $838万
 $25,382/呎
-(25年-06月-23日)</t>
+(25年-06月-24日)</t>
         </is>
       </c>
     </row>
@@ -26102,7 +26102,7 @@
           <t>A | 524呎 (2房)
 $1242万
 $23,702/呎
-(25年-07月-07日)</t>
+(25年-07月-08日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -26110,7 +26110,7 @@
           <t>B | 315呎 (1房)
 $806万
 $25,578/呎
-(25年-07月-07日)</t>
+(25年-07月-08日)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -26118,7 +26118,7 @@
           <t>C | 318呎 (1房)
 $935万
 $29,415/呎
-(21年-07月-22日)</t>
+(21年-07月-23日)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -26126,7 +26126,7 @@
           <t>D | 330呎 (1房)
 $820万
 $24,855/呎
-(25年-06月-22日)</t>
+(25年-06月-23日)</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
@@ -26134,7 +26134,7 @@
           <t>E | 278呎 (开放式)
 $763万
 $27,441/呎
-(21年-11月-01日)</t>
+(21年-11月-02日)</t>
         </is>
       </c>
       <c r="G12" s="20" t="inlineStr">
@@ -26142,7 +26142,7 @@
           <t>F | 278呎 (开放式)
 $663万
 $23,853/呎
-(25年-06月-25日)</t>
+(25年-06月-26日)</t>
         </is>
       </c>
       <c r="H12" s="20" t="inlineStr">
@@ -26150,7 +26150,7 @@
           <t>G | 330呎 (1房)
 $833万
 $25,256/呎
-(25年-06月-26日)</t>
+(25年-06月-27日)</t>
         </is>
       </c>
     </row>
@@ -26165,7 +26165,7 @@
           <t>A | 524呎 (2房)
 $1239万
 $23,651/呎
-(25年-06月-22日)</t>
+(25年-06月-23日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -26173,7 +26173,7 @@
           <t>B | 315呎 (1房)
 $905万
 $28,716/呎
-(22年-04月-24日)</t>
+(22年-04月-25日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -26181,7 +26181,7 @@
           <t>C | 318呎 (1房)
 $815万
 $25,632/呎
-(25年-06月-23日)</t>
+(25年-06月-24日)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -26189,7 +26189,7 @@
           <t>D | 330呎 (1房)
 $816万
 $24,732/呎
-(25年-06月-22日)</t>
+(25年-06月-23日)</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
@@ -26197,7 +26197,7 @@
           <t>E | 277呎 (开放式)
 $759万
 $27,403/呎
-(21年-09月-14日)</t>
+(21年-09月-15日)</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr">
@@ -26205,7 +26205,7 @@
           <t>F | 278呎 (开放式)
 $660万
 $23,733/呎
-(25年-06月-25日)</t>
+(25年-06月-26日)</t>
         </is>
       </c>
       <c r="H13" s="20" t="inlineStr">
@@ -26213,7 +26213,7 @@
           <t>G | 330呎 (1房)
 $829万
 $25,128/呎
-(25年-06月-22日)</t>
+(25年-06月-23日)</t>
         </is>
       </c>
     </row>
@@ -26228,7 +26228,7 @@
           <t>A | 524呎 (2房)
 $1233万
 $23,531/呎
-(24年-12月-29日)</t>
+(24年-12月-30日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -26236,7 +26236,7 @@
           <t>B | 315呎 (1房)
 $798万
 $25,322/呎
-(25年-06月-19日)</t>
+(25年-06月-20日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -26244,7 +26244,7 @@
           <t>C | 318呎 (1房)
 $926万
 $29,123/呎
-(21年-09月-23日)</t>
+(21年-09月-24日)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -26252,7 +26252,7 @@
           <t>D | 330呎 (1房)
 $812万
 $24,608/呎
-(25年-06月-19日)</t>
+(25年-06月-20日)</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
@@ -26260,7 +26260,7 @@
           <t>E | 278呎 (开放式)
 $755万
 $27,171/呎
-(21年-09月-17日)</t>
+(21年-09月-18日)</t>
         </is>
       </c>
       <c r="G14" s="20" t="inlineStr">
@@ -26268,7 +26268,7 @@
           <t>F | 278呎 (开放式)
 $657万
 $23,619/呎
-(25年-07月-24日)</t>
+(25年-07月-25日)</t>
         </is>
       </c>
       <c r="H14" s="20" t="inlineStr">
@@ -26276,7 +26276,7 @@
           <t>G | 330呎 (1房)
 $903万
 $27,368/呎
-(25年-05月-07日)</t>
+(25年-05月-08日)</t>
         </is>
       </c>
     </row>
@@ -26291,7 +26291,7 @@
           <t>A | 524呎 (2房)
 $1222万
 $23,321/呎
-(25年-06月-03日)</t>
+(25年-06月-04日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -26299,7 +26299,7 @@
           <t>B | 315呎 (1房)
 $906万
 $28,770/呎
-(22年-01月-16日)</t>
+(22年-01月-17日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -26307,7 +26307,7 @@
           <t>C | 318呎 (1房)
 $883万
 $27,777/呎
-(21年-09月-23日)</t>
+(21年-09月-24日)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -26315,7 +26315,7 @@
           <t>D | 330呎 (1房)
 $885万
 $26,804/呎
-(24年-01月-11日)</t>
+(24年-01月-12日)</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
@@ -26323,7 +26323,7 @@
           <t>E | 278呎 (开放式)
 $752万
 $27,034/呎
-(21年-10月-07日)</t>
+(21年-10月-08日)</t>
         </is>
       </c>
       <c r="G15" s="20" t="inlineStr">
@@ -26331,7 +26331,7 @@
           <t>F | 278呎 (开放式)
 $653万
 $23,499/呎
-(25年-07月-16日)</t>
+(25年-07月-17日)</t>
         </is>
       </c>
       <c r="H15" s="20" t="inlineStr">
@@ -26339,7 +26339,7 @@
           <t>G | 331呎 (1房)
 $926万
 $27,989/呎
-(22年-06月-28日)</t>
+(22年-06月-29日)</t>
         </is>
       </c>
     </row>
@@ -26354,7 +26354,7 @@
           <t>A | 524呎 (2房)
 $1220万
 $23,282/呎
-(25年-03月-27日)</t>
+(25年-03月-28日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -26362,7 +26362,7 @@
           <t>B | 315呎 (1房)
 $902万
 $28,630/呎
-(21年-11月-15日)</t>
+(21年-11月-16日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -26370,7 +26370,7 @@
           <t>C | 318呎 (1房)
 $803万
 $25,251/呎
-(25年-06月-24日)</t>
+(25年-06月-25日)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -26378,7 +26378,7 @@
           <t>D | 330呎 (1房)
 $804万
 $24,364/呎
-(25年-06月-25日)</t>
+(25年-06月-26日)</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
@@ -26386,7 +26386,7 @@
           <t>E | 278呎 (开放式)
 $717万
 $25,786/呎
-(26年-04月-15日)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -26394,7 +26394,7 @@
           <t>F | 278呎 (开放式)
 $712万
 $25,594/呎
-(23年-03月-19日)</t>
+(23年-03月-20日)</t>
         </is>
       </c>
       <c r="H16" s="20" t="inlineStr">
@@ -26402,7 +26402,7 @@
           <t>G | 330呎 (1房)
 $817万
 $24,756/呎
-(25年-06月-24日)</t>
+(25年-06月-25日)</t>
         </is>
       </c>
     </row>
@@ -26417,7 +26417,7 @@
           <t>A | 524呎 (2房)
 $1215万
 $23,187/呎
-(24年-12月-26日)</t>
+(24年-12月-27日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -26425,7 +26425,7 @@
           <t>B | 315呎 (1房)
 $786万
 $24,946/呎
-(25年-06月-22日)</t>
+(25年-06月-23日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -26433,7 +26433,7 @@
           <t>C | 317呎 (1房)
 $912万
 $28,783/呎
-(21年-08月-12日)</t>
+(21年-08月-13日)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -26441,7 +26441,7 @@
           <t>D | 331呎 (1房)
 $876万
 $26,456/呎
-(23年-07月-13日)</t>
+(23年-07月-14日)</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -26449,7 +26449,7 @@
           <t>E | 277呎 (开放式)
 $744万
 $26,863/呎
-(21年-09月-28日)</t>
+(21年-09月-29日)</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
@@ -26457,7 +26457,7 @@
           <t>F | 278呎 (开放式)
 $739万
 $26,566/呎
-(22年-02月-16日)</t>
+(22年-02月-17日)</t>
         </is>
       </c>
       <c r="H17" s="20" t="inlineStr">
@@ -26465,7 +26465,7 @@
           <t>G | 330呎 (1房)
 $890万
 $26,963/呎
-(24年-12月-18日)</t>
+(24年-12月-19日)</t>
         </is>
       </c>
     </row>
@@ -26480,7 +26480,7 @@
           <t>A | 524呎 (2房)
 $1208万
 $23,053/呎
-(25年-01月-13日)</t>
+(25年-01月-14日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -26488,7 +26488,7 @@
           <t>B | 315呎 (1房)
 $897万
 $28,486/呎
-(21年-09月-26日)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -26496,7 +26496,7 @@
           <t>C | 317呎 (1房)
 $912万
 $28,783/呎
-(21年-08月-03日)</t>
+(21年-08月-04日)</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -26504,7 +26504,7 @@
           <t>D | 330呎 (1房)
 $876万
 $26,536/呎
-(21年-11月-17日)</t>
+(21年-11月-18日)</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -26512,7 +26512,7 @@
           <t>E | 278呎 (开放式)
 $713万
 $25,658/呎
-(26年-04月-28日)</t>
+(26年-04月-29日)</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
@@ -26520,7 +26520,7 @@
           <t>F | 278呎 (开放式)
 $739万
 $26,566/呎
-(21年-11月-29日)</t>
+(21年-11月-30日)</t>
         </is>
       </c>
       <c r="H18" s="20" t="inlineStr">
@@ -26528,7 +26528,7 @@
           <t>G | 330呎 (1房)
 $813万
 $24,633/呎
-(25年-06月-19日)</t>
+(25年-06月-20日)</t>
         </is>
       </c>
     </row>
@@ -26543,7 +26543,7 @@
           <t>A | 524呎 (2房)
 $1206万
 $23,015/呎
-(24年-12月-02日)</t>
+(24年-12月-03日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -26551,7 +26551,7 @@
           <t>B | 315呎 (1房)
 $778万
 $24,699/呎
-(25年-06月-22日)</t>
+(25年-06月-23日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -26559,7 +26559,7 @@
           <t>C | 318呎 (1房)
 $866万
 $27,229/呎
-(21年-08月-01日)</t>
+(21年-08月-02日)</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -26567,7 +26567,7 @@
           <t>D | 331呎 (1房)
 $867万
 $26,194/呎
-(22年-05月-05日)</t>
+(22年-05月-06日)</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
@@ -26575,7 +26575,7 @@
           <t>E | 278呎 (开放式)
 $737万
 $26,502/呎
-(21年-08月-11日)</t>
+(21年-08月-12日)</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
@@ -26583,7 +26583,7 @@
           <t>F | 278呎 (开放式)
 $701万
 $25,215/呎
-(22年-01月-13日)</t>
+(22年-01月-14日)</t>
         </is>
       </c>
       <c r="H19" s="20" t="inlineStr">
@@ -26591,7 +26591,7 @@
           <t>G | 331呎 (1房)
 $908万
 $27,436/呎
-(22年-05月-16日)</t>
+(22年-05月-17日)</t>
         </is>
       </c>
     </row>
@@ -26606,7 +26606,7 @@
           <t>A | 524呎 (2房)
 $1200万
 $22,901/呎
-(24年-11月-20日)</t>
+(24年-11月-21日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -26614,7 +26614,7 @@
           <t>B | 315呎 (1房)
 $884万
 $28,062/呎
-(21年-09月-14日)</t>
+(21年-09月-15日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -26622,7 +26622,7 @@
           <t>C | 318呎 (1房)
 $851万
 $26,762/呎
-(21年-04月-27日)</t>
+(21年-04月-28日)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -26630,7 +26630,7 @@
           <t>D | 330呎 (1房)
 $900万
 $27,273/呎
-(21年-11月-10日)</t>
+(21年-11月-11日)</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -26638,7 +26638,7 @@
           <t>E | 277呎 (开放式)
 $694万
 $25,054/呎
-(21年-04月-22日)</t>
+(21年-04月-23日)</t>
         </is>
       </c>
       <c r="G20" s="20" t="inlineStr">
@@ -26646,7 +26646,7 @@
           <t>F | 278呎 (开放式)
 $697万
 $25,090/呎
-(21年-11月-09日)</t>
+(21年-11月-10日)</t>
         </is>
       </c>
       <c r="H20" s="20" t="inlineStr">
@@ -26654,7 +26654,7 @@
           <t>G | 330呎 (1房)
 $877万
 $26,565/呎
-(21年-11月-14日)</t>
+(21年-11月-15日)</t>
         </is>
       </c>
     </row>
@@ -26669,7 +26669,7 @@
           <t>A | 524呎 (2房)
 $1193万
 $22,764/呎
-(24年-10月-20日)</t>
+(24年-10月-21日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -26677,7 +26677,7 @@
           <t>B | 315呎 (1房)
 $880万
 $27,923/呎
-(21年-09月-15日)</t>
+(21年-09月-16日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -26685,7 +26685,7 @@
           <t>C | 317呎 (1房)
 $894万
 $28,213/呎
-(21年-08月-08日)</t>
+(21年-08月-09日)</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
@@ -26693,7 +26693,7 @@
           <t>D | 330呎 (1房)
 $896万
 $27,137/呎
-(21年-11月-11日)</t>
+(21年-11月-12日)</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -26701,7 +26701,7 @@
           <t>E | 277呎 (开放式)
 $729万
 $26,335/呎
-(21年-08月-10日)</t>
+(21年-08月-11日)</t>
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr">
@@ -26709,7 +26709,7 @@
           <t>F | 278呎 (开放式)
 $694万
 $24,964/呎
-(21年-11月-25日)</t>
+(21年-11月-26日)</t>
         </is>
       </c>
       <c r="H21" s="20" t="inlineStr">
@@ -26717,7 +26717,7 @@
           <t>G | 331呎 (1房)
 $797万
 $24,073/呎
-(25年-06月-15日)</t>
+(25年-06月-16日)</t>
         </is>
       </c>
     </row>
@@ -26732,7 +26732,7 @@
           <t>A | 524呎 (2房)
 $1183万
 $22,576/呎
-(24年-11月-04日)</t>
+(24年-11月-05日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -26740,7 +26740,7 @@
           <t>B | 315呎 (1房)
 $839万
 $26,635/呎
-(21年-09月-20日)</t>
+(21年-09月-21日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -26748,7 +26748,7 @@
           <t>C | 317呎 (1房)
 $879万
 $27,739/呎
-(21年-07月-07日)</t>
+(21年-07月-08日)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -26756,7 +26756,7 @@
           <t>D | 331呎 (1房)
 $854万
 $25,805/呎
-(21年-10月-22日)</t>
+(21年-10月-23日)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
@@ -26764,7 +26764,7 @@
           <t>E | 277呎 (开放式)
 $717万
 $25,891/呎
-(21年-07月-01日)</t>
+(21年-07月-02日)</t>
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr">
@@ -26772,7 +26772,7 @@
           <t>F | 278呎 (开放式)
 $720万
 $25,912/呎
-(21年-11月-25日)</t>
+(21年-11月-26日)</t>
         </is>
       </c>
       <c r="H22" s="20" t="inlineStr">
@@ -26780,7 +26780,7 @@
           <t>G | 331呎 (1房)
 $905万
 $27,354/呎
-(21年-11月-18日)</t>
+(21年-11月-19日)</t>
         </is>
       </c>
     </row>
@@ -26795,7 +26795,7 @@
           <t>A | 524呎 (2房)
 $1173万
 $22,385/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -26803,7 +26803,7 @@
           <t>B | 315呎 (1房)
 $871万
 $27,646/呎
-(21年-09月-06日)</t>
+(21年-09月-07日)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -26811,7 +26811,7 @@
           <t>C | 317呎 (1房)
 $885万
 $27,933/呎
-(21年-08月-05日)</t>
+(21年-08月-06日)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
@@ -26819,7 +26819,7 @@
           <t>D | 331呎 (1房)
 $887万
 $26,787/呎
-(21年-11月-03日)</t>
+(21年-11月-04日)</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -26827,7 +26827,7 @@
           <t>E | 277呎 (开放式)
 $714万
 $25,761/呎
-(21年-04月-20日)</t>
+(21年-04月-21日)</t>
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr">
@@ -26835,7 +26835,7 @@
           <t>F | 278呎 (开放式)
 $649万
 $23,343/呎
-(25年-07月-17日)</t>
+(25年-07月-18日)</t>
         </is>
       </c>
       <c r="H23" s="20" t="inlineStr">
@@ -26843,7 +26843,7 @@
           <t>G | 330呎 (1房)
 $789万
 $23,906/呎
-(25年-06月-23日)</t>
+(25年-06月-24日)</t>
         </is>
       </c>
     </row>
@@ -26858,7 +26858,7 @@
           <t>A | 524呎 (2房)
 $1160万
 $22,137/呎
-(24年-11月-14日)</t>
+(24年-11月-15日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -26866,7 +26866,7 @@
           <t>B | 315呎 (1房)
 $759万
 $24,091/呎
-(25年-06月-19日)</t>
+(25年-06月-20日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -26874,7 +26874,7 @@
           <t>C | 317呎 (1房)
 $881万
 $27,791/呎
-(21年-08月-04日)</t>
+(21年-08月-05日)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -26882,7 +26882,7 @@
           <t>D | 330呎 (1房)
 $846万
 $25,628/呎
-(21年-10月-31日)</t>
+(21年-11月-01日)</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
@@ -26890,7 +26890,7 @@
           <t>E | 278呎 (开放式)
 $689万
 $24,778/呎
-(26年-04月-22日)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr">
@@ -26898,7 +26898,7 @@
           <t>F | 278呎 (开放式)
 $713万
 $25,657/呎
-(21年-11月-10日)</t>
+(21年-11月-11日)</t>
         </is>
       </c>
       <c r="H24" s="20" t="inlineStr">
@@ -26906,7 +26906,7 @@
           <t>G | 330呎 (1房)
 $859万
 $26,040/呎
-(21年-09月-23日)</t>
+(21年-09月-24日)</t>
         </is>
       </c>
     </row>
@@ -26921,7 +26921,7 @@
           <t>A | 524呎 (2房)
 $1150万
 $21,947/呎
-(24年-11月-24日)</t>
+(24年-11月-25日)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -26929,7 +26929,7 @@
           <t>B | 315呎 (1房)
 $755万
 $23,971/呎
-(25年-06月-19日)</t>
+(25年-06月-20日)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -26937,7 +26937,7 @@
           <t>C | 318呎 (1房)
 $866万
 $27,242/呎
-(21年-04月-26日)</t>
+(21年-04月-27日)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
@@ -26945,7 +26945,7 @@
           <t>D | 330呎 (1房)
 $769万
 $23,296/呎
-(25年-06月-19日)</t>
+(25年-06月-20日)</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -26953,7 +26953,7 @@
           <t>E | 278呎 (开放式)
 $685万
 $24,653/呎
-(26年-04月-08日)</t>
+(26年-04月-09日)</t>
         </is>
       </c>
       <c r="G25" s="20" t="inlineStr">
@@ -26961,7 +26961,7 @@
           <t>F | 278呎 (开放式)
 $710万
 $25,529/呎
-(21年-11月-21日)</t>
+(21年-11月-22日)</t>
         </is>
       </c>
       <c r="H25" s="20" t="inlineStr">
@@ -26969,7 +26969,7 @@
           <t>G | 330呎 (1房)
 $896万
 $27,165/呎
-(21年-09月-22日)</t>
+(21年-09月-23日)</t>
         </is>
       </c>
     </row>
@@ -26984,7 +26984,7 @@
           <t>A | 524呎 (2房)
 $1148万
 $21,908/呎
-(24年-11月-21日)</t>
+(24年-11月-22日)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -26992,7 +26992,7 @@
           <t>B | 315呎 (1房)
 $862万
 $27,372/呎
-(21年-08月-19日)</t>
+(21年-08月-20日)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -27000,7 +27000,7 @@
           <t>C | 317呎 (1房)
 $866万
 $27,328/呎
-(21年-05月-12日)</t>
+(21年-05月-13日)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
@@ -27008,7 +27008,7 @@
           <t>D | 330呎 (1房)
 $842万
 $25,500/呎
-(21年-09月-24日)</t>
+(21年-09月-25日)</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
@@ -27016,7 +27016,7 @@
           <t>E | 278呎 (开放式)
 $706万
 $25,413/呎
-(21年-06月-28日)</t>
+(21年-06月-29日)</t>
         </is>
       </c>
       <c r="G26" s="20" t="inlineStr">
@@ -27024,7 +27024,7 @@
           <t>F | 278呎 (开放式)
 $647万
 $23,263/呎
-(25年-07月-10日)</t>
+(25年-07月-11日)</t>
         </is>
       </c>
       <c r="H26" s="20" t="inlineStr">
@@ -27032,7 +27032,7 @@
           <t>G | 331呎 (1房)
 $888万
 $26,813/呎
-(21年-10月-21日)</t>
+(21年-10月-22日)</t>
         </is>
       </c>
     </row>
@@ -27047,7 +27047,7 @@
           <t>A | 524呎 (2房)
 $1284万
 $24,507/呎
-(23年-04月-23日)</t>
+(23年-04月-24日)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -27055,7 +27055,7 @@
           <t>B | 315呎 (1房)
 $818万
 $25,979/呎
-(21年-07月-23日)</t>
+(21年-07月-24日)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -27063,7 +27063,7 @@
           <t>C | 317呎 (1房)
 $868万
 $27,384/呎
-(21年-07月-08日)</t>
+(21年-07月-09日)</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr">
@@ -27071,7 +27071,7 @@
           <t>D | 330呎 (1房)
 $761万
 $23,065/呎
-(25年-06月-23日)</t>
+(25年-06月-24日)</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
@@ -27079,7 +27079,7 @@
           <t>E | 277呎 (开放式)
 $700万
 $25,255/呎
-(21年-07月-08日)</t>
+(21年-07月-09日)</t>
         </is>
       </c>
       <c r="G27" s="20" t="inlineStr">
@@ -27087,7 +27087,7 @@
           <t>F | 278呎 (开放式)
 $674万
 $24,227/呎
-(21年-10月-28日)</t>
+(21年-10月-29日)</t>
         </is>
       </c>
       <c r="H27" s="20" t="inlineStr">
@@ -27095,7 +27095,7 @@
           <t>G | 330呎 (1房)
 $847万
 $25,652/呎
-(21年-09月-22日)</t>
+(21年-09月-23日)</t>
         </is>
       </c>
     </row>
@@ -27110,7 +27110,7 @@
           <t>A | 524呎 (2房)
 $1140万
 $21,756/呎
-(24年-11月-27日)</t>
+(24年-11月-28日)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -27118,7 +27118,7 @@
           <t>B | 315呎 (1房)
 $849万
 $26,967/呎
-(21年-08月-12日)</t>
+(21年-08月-13日)</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -27126,7 +27126,7 @@
           <t>C | 317呎 (1房)
 $853万
 $26,923/呎
-(21年-04月-20日)</t>
+(21年-04月-21日)</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
@@ -27134,7 +27134,7 @@
           <t>D | 331呎 (1房)
 $844万
 $25,510/呎
-(21年-09月-30日)</t>
+(21年-10月-01日)</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
@@ -27142,7 +27142,7 @@
           <t>E | 277呎 (开放式)
 $675万
 $24,376/呎
-(21年-07月-05日)</t>
+(21年-07月-06日)</t>
         </is>
       </c>
       <c r="G28" s="20" t="inlineStr">
@@ -27150,7 +27150,7 @@
           <t>F | 278呎 (开放式)
 $670万
 $24,108/呎
-(21年-11月-16日)</t>
+(21年-11月-17日)</t>
         </is>
       </c>
       <c r="H28" s="20" t="inlineStr">
@@ -27158,7 +27158,7 @@
           <t>G | 330呎 (1房)
 $879万
 $26,628/呎
-(21年-09月-14日)</t>
+(21年-09月-15日)</t>
         </is>
       </c>
     </row>
@@ -27173,7 +27173,7 @@
           <t>A | 524呎 (2房)
 $1130万
 $21,565/呎
-(24年-12月-04日)</t>
+(24年-12月-05日)</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
@@ -27181,7 +27181,7 @@
           <t>B | 315呎 (1房)
 $848万
 $26,914/呎
-(21年-08月-29日)</t>
+(21年-08月-30日)</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
@@ -27189,7 +27189,7 @@
           <t>C | 317呎 (1房)
 $862万
 $27,192/呎
-(21年-08月-11日)</t>
+(21年-08月-12日)</t>
         </is>
       </c>
       <c r="E29" s="20" t="inlineStr">
@@ -27197,7 +27197,7 @@
           <t>D | 330呎 (1房)
 $863万
 $26,154/呎
-(21年-11月-08日)</t>
+(21年-11月-09日)</t>
         </is>
       </c>
       <c r="F29" s="20" t="inlineStr">
@@ -27205,7 +27205,7 @@
           <t>E | 278呎 (开放式)
 $703万
 $25,286/呎
-(21年-10月-20日)</t>
+(21年-10月-21日)</t>
         </is>
       </c>
       <c r="G29" s="20" t="inlineStr">
@@ -27213,7 +27213,7 @@
           <t>F | 278呎 (开放式)
 $669万
 $24,061/呎
-(24年-04月-10日)</t>
+(24年-04月-11日)</t>
         </is>
       </c>
       <c r="H29" s="20" t="inlineStr">
@@ -27221,7 +27221,7 @@
           <t>G | 331呎 (1房)
 $867万
 $26,180/呎
-(22年-04月-21日)</t>
+(22年-04月-22日)</t>
         </is>
       </c>
     </row>
@@ -27236,7 +27236,7 @@
           <t>A | 524呎 (2房)
 $1125万
 $21,469/呎
-(24年-12月-03日)</t>
+(24年-12月-04日)</t>
         </is>
       </c>
       <c r="C30" s="20" t="inlineStr">
@@ -27244,7 +27244,7 @@
           <t>B | 315呎 (1房)
 $846万
 $26,860/呎
-(21年-09月-02日)</t>
+(21年-09月-03日)</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
@@ -27252,7 +27252,7 @@
           <t>C | 318呎 (1房)
 $860万
 $27,051/呎
-(21年-08月-16日)</t>
+(21年-08月-17日)</t>
         </is>
       </c>
       <c r="E30" s="20" t="inlineStr">
@@ -27260,7 +27260,7 @@
           <t>D | 331呎 (1房)
 $826万
 $24,946/呎
-(21年-11月-09日)</t>
+(21年-11月-10日)</t>
         </is>
       </c>
       <c r="F30" s="20" t="inlineStr">
@@ -27268,7 +27268,7 @@
           <t>E | 277呎 (开放式)
 $702万
 $25,329/呎
-(21年-10月-27日)</t>
+(21年-10月-28日)</t>
         </is>
       </c>
       <c r="G30" s="20" t="inlineStr">
@@ -27276,7 +27276,7 @@
           <t>F | 278呎 (开放式)
 $668万
 $24,012/呎
-(24年-06月-04日)</t>
+(24年-06月-05日)</t>
         </is>
       </c>
       <c r="H30" s="20" t="inlineStr">
@@ -27284,7 +27284,7 @@
           <t>G | 330呎 (1房)
 $839万
 $25,424/呎
-(22年-05月-04日)</t>
+(22年-05月-05日)</t>
         </is>
       </c>
     </row>
@@ -27299,7 +27299,7 @@
           <t>A | 524呎 (2房)
 $1121万
 $21,401/呎
-(24年-11月-24日)</t>
+(24年-11月-25日)</t>
         </is>
       </c>
       <c r="C31" s="20" t="inlineStr">
@@ -27307,7 +27307,7 @@
           <t>B | 315呎 (1房)
 $809万
 $25,696/呎
-(21年-08月-26日)</t>
+(21年-08月-27日)</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">
@@ -27315,7 +27315,7 @@
           <t>C | 317呎 (1房)
 $823万
 $25,961/呎
-(21年-09月-20日)</t>
+(21年-09月-21日)</t>
         </is>
       </c>
       <c r="E31" s="20" t="inlineStr">
@@ -27323,7 +27323,7 @@
           <t>D | 330呎 (1房)
 $850万
 $25,743/呎
-(22年-06月-01日)</t>
+(22年-06月-02日)</t>
         </is>
       </c>
       <c r="F31" s="20" t="inlineStr">
@@ -27331,7 +27331,7 @@
           <t>E | 277呎 (开放式)
 $700万
 $25,277/呎
-(21年-10月-31日)</t>
+(21年-11月-01日)</t>
         </is>
       </c>
       <c r="G31" s="20" t="inlineStr">
@@ -27339,7 +27339,7 @@
           <t>F | 278呎 (开放式)
 $666万
 $23,965/呎
-(25年-01月-07日)</t>
+(25年-01月-08日)</t>
         </is>
       </c>
       <c r="H31" s="20" t="inlineStr">
@@ -27347,7 +27347,7 @@
           <t>G | 330呎 (1房)
 $863万
 $26,153/呎
-(22年-05月-30日)</t>
+(22年-05月-31日)</t>
         </is>
       </c>
     </row>
@@ -27362,7 +27362,7 @@
           <t>A | 487呎 (2房)
 $1500万
 $30,801/呎
-(24年-04月-16日)</t>
+(24年-04月-17日)</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
@@ -27370,7 +27370,7 @@
           <t>B | 294呎 (1房)
 $810万
 $27,551/呎
-(24年-10月-16日)</t>
+(24年-10月-17日)</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">
@@ -27378,7 +27378,7 @@
           <t>C | 296呎 (1房)
 $815万
 $27,534/呎
-(24年-10月-17日)</t>
+(24年-10月-18日)</t>
         </is>
       </c>
       <c r="E32" s="20" t="inlineStr">
@@ -27386,7 +27386,7 @@
           <t>D | 309呎 (1房)
 $838万
 $27,120/呎
-(24年-10月-23日)</t>
+(24年-10月-24日)</t>
         </is>
       </c>
       <c r="F32" s="20" t="inlineStr">
@@ -27394,7 +27394,7 @@
           <t>E | 256呎 (开放式)
 $633万
 $24,727/呎
-(24年-11月-03日)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="G32" s="20" t="inlineStr">
@@ -27402,7 +27402,7 @@
           <t>F | 256呎 (开放式)
 $628万
 $24,531/呎
-(24年-11月-03日)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="H32" s="20" t="inlineStr">
@@ -27410,7 +27410,7 @@
           <t>G | 309呎 (1房)
 $853万
 $27,600/呎
-(24年-10月-16日)</t>
+(24年-10月-17日)</t>
         </is>
       </c>
     </row>
@@ -27554,7 +27554,7 @@
           <t>A | 584呎 (2房)
 $1505万
 $25,765/呎
-(24年-11月-14日)</t>
+(24年-11月-15日)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
@@ -27562,7 +27562,7 @@
           <t>B | 312呎 (1房)
 $817万
 $26,173/呎
-(25年-06月-23日)</t>
+(25年-06月-24日)</t>
         </is>
       </c>
       <c r="D5" s="20" t="inlineStr">
@@ -27570,7 +27570,7 @@
           <t>C | 449呎 (2房)
 $1293万
 $28,797/呎
-(25年-05月-18日)</t>
+(25年-05月-19日)</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr">
@@ -27578,7 +27578,7 @@
           <t>D | 311呎 (1房)
 $866万
 $27,851/呎
-(25年-06月-23日)</t>
+(25年-06月-24日)</t>
         </is>
       </c>
       <c r="F5" s="20" t="inlineStr">
@@ -27586,7 +27586,7 @@
           <t>E | 525呎 (2房)
 $1459万
 $27,785/呎
-(24年-11月-26日)</t>
+(24年-11月-27日)</t>
         </is>
       </c>
     </row>
@@ -27601,7 +27601,7 @@
           <t>A | 584呎 (2房)
 $1475万
 $25,261/呎
-(24年-11月-14日)</t>
+(24年-11月-15日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -27609,7 +27609,7 @@
           <t>B | 312呎 (1房)
 $876万
 $28,088/呎
-(24年-03月-19日)</t>
+(24年-03月-20日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -27617,7 +27617,7 @@
           <t>C | 449呎 (2房)
 $1282万
 $28,559/呎
-(24年-12月-11日)</t>
+(24年-12月-12日)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -27625,7 +27625,7 @@
           <t>D | 311呎 (1房)
 $930万
 $29,889/呎
-(23年-02月-22日)</t>
+(23年-02月-23日)</t>
         </is>
       </c>
       <c r="F6" s="20" t="inlineStr">
@@ -27633,7 +27633,7 @@
           <t>E | 525呎 (2房)
 $1430万
 $27,239/呎
-(24年-11月-18日)</t>
+(24年-11月-19日)</t>
         </is>
       </c>
     </row>
@@ -27648,7 +27648,7 @@
           <t>A | 584呎 (2房)
 $1461万
 $25,011/呎
-(24年-10月-24日)</t>
+(24年-10月-25日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -27656,7 +27656,7 @@
           <t>B | 312呎 (1房)
 $894万
 $28,665/呎
-(22年-03月-31日)</t>
+(22年-04月-01日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -27664,7 +27664,7 @@
           <t>C | 449呎 (2房)
 $1265万
 $28,174/呎
-(25年-03月-09日)</t>
+(25年-03月-10日)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -27672,7 +27672,7 @@
           <t>D | 311呎 (1房)
 $841万
 $27,037/呎
-(25年-07月-07日)</t>
+(25年-07月-08日)</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">
@@ -27680,7 +27680,7 @@
           <t>E | 525呎 (2房)
 $1416万
 $26,971/呎
-(24年-08月-04日)</t>
+(24年-08月-05日)</t>
         </is>
       </c>
     </row>
@@ -27695,7 +27695,7 @@
           <t>A | 584呎 (2房)
 $1410万
 $24,140/呎
-(24年-09月-03日)</t>
+(24年-09月-04日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -27703,7 +27703,7 @@
           <t>B | 312呎 (1房)
 $789万
 $25,281/呎
-(25年-06月-01日)</t>
+(25年-06月-02日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -27711,7 +27711,7 @@
           <t>C | 449呎 (2房)
 $1263万
 $28,135/呎
-(24年-06月-03日)</t>
+(24年-06月-04日)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -27719,7 +27719,7 @@
           <t>D | 311呎 (1房)
 $837万
 $26,902/呎
-(25年-06月-26日)</t>
+(25年-06月-27日)</t>
         </is>
       </c>
       <c r="F8" s="20" t="inlineStr">
@@ -27727,7 +27727,7 @@
           <t>E | 525呎 (2房)
 $1409万
 $26,836/呎
-(24年-06月-03日)</t>
+(24年-06月-04日)</t>
         </is>
       </c>
     </row>
@@ -27742,7 +27742,7 @@
           <t>A | 584呎 (2房)
 $1453万
 $24,885/呎
-(24年-10月-24日)</t>
+(24年-10月-25日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -27750,7 +27750,7 @@
           <t>B | 312呎 (1房)
 $901万
 $28,868/呎
-(21年-09月-09日)</t>
+(21年-09月-10日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -27758,7 +27758,7 @@
           <t>C | 449呎 (2房)
 $1263万
 $28,135/呎
-(24年-08月-13日)</t>
+(24年-08月-14日)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -27766,7 +27766,7 @@
           <t>D | 311呎 (1房)
 $837万
 $26,902/呎
-(25年-07月-02日)</t>
+(25年-07月-03日)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -27774,7 +27774,7 @@
           <t>E | 525呎 (2房)
 $1409万
 $26,836/呎
-(24年-08月-20日)</t>
+(24年-08月-21日)</t>
         </is>
       </c>
     </row>
@@ -27789,7 +27789,7 @@
           <t>A | 584呎 (2房)
 $1439万
 $24,640/呎
-(24年-08月-13日)</t>
+(24年-08月-14日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -27797,7 +27797,7 @@
           <t>B | 312呎 (1房)
 $892万
 $28,581/呎
-(21年-10月-04日)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -27805,7 +27805,7 @@
           <t>C | 449呎 (2房)
 $1238万
 $27,572/呎
-(25年-01月-23日)</t>
+(25年-01月-24日)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -27813,7 +27813,7 @@
           <t>D | 311呎 (1房)
 $907万
 $29,155/呎
-(24年-01月-07日)</t>
+(24年-01月-08日)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -27821,7 +27821,7 @@
           <t>E | 525呎 (2房)
 $1395万
 $26,570/呎
-(24年-11月-05日)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
     </row>
@@ -27836,7 +27836,7 @@
           <t>A | 584呎 (2房)
 $1389万
 $23,784/呎
-(24年-07月-28日)</t>
+(24年-07月-29日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -27844,7 +27844,7 @@
           <t>B | 312呎 (1房)
 $887万
 $28,438/呎
-(21年-09月-12日)</t>
+(21年-09月-13日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -27852,7 +27852,7 @@
           <t>C | 449呎 (2房)
 $1245万
 $27,718/呎
-(24年-08月-12日)</t>
+(24年-08月-13日)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -27860,7 +27860,7 @@
           <t>D | 311呎 (1房)
 $941万
 $30,265/呎
-(21年-11月-09日)</t>
+(21年-11月-10日)</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
@@ -27868,7 +27868,7 @@
           <t>E | 525呎 (2房)
 $1388万
 $26,438/呎
-(24年-09月-29日)</t>
+(24年-09月-30日)</t>
         </is>
       </c>
     </row>
@@ -27883,7 +27883,7 @@
           <t>A | 584呎 (2房)
 $1425万
 $24,394/呎
-(24年-08月-11日)</t>
+(24年-08月-12日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -27891,7 +27891,7 @@
           <t>B | 312呎 (1房)
 $883万
 $28,296/呎
-(21年-08月-29日)</t>
+(21年-08月-30日)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -27899,7 +27899,7 @@
           <t>C | 449呎 (2房)
 $1230万
 $27,394/呎
-(25年-01月-16日)</t>
+(25年-01月-17日)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -27907,7 +27907,7 @@
           <t>D | 311呎 (1房)
 $820万
 $26,371/呎
-(25年-06月-26日)</t>
+(25年-06月-27日)</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
@@ -27915,7 +27915,7 @@
           <t>E | 525呎 (2房)
 $1381万
 $26,307/呎
-(24年-10月-21日)</t>
+(24年-10月-22日)</t>
         </is>
       </c>
     </row>
@@ -27930,7 +27930,7 @@
           <t>A | 584呎 (2房)
 $1417万
 $24,272/呎
-(24年-06月-20日)</t>
+(24年-06月-21日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -27938,7 +27938,7 @@
           <t>B | 312呎 (1房)
 $878万
 $28,156/呎
-(21年-08月-10日)</t>
+(21年-08月-11日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -27946,7 +27946,7 @@
           <t>C | 449呎 (2房)
 $1232万
 $27,444/呎
-(24年-06月-27日)</t>
+(24年-06月-28日)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -27954,7 +27954,7 @@
           <t>D | 311呎 (1房)
 $893万
 $28,722/呎
-(21年-10月-11日)</t>
+(21年-10月-12日)</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
@@ -27962,7 +27962,7 @@
           <t>E | 525呎 (2房)
 $1374万
 $26,176/呎
-(24年-11月-28日)</t>
+(24年-11月-29日)</t>
         </is>
       </c>
     </row>
@@ -27977,7 +27977,7 @@
           <t>A | 584呎 (2房)
 $1411万
 $24,153/呎
-(24年-06月-19日)</t>
+(24年-06月-20日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -27985,7 +27985,7 @@
           <t>B | 312呎 (1房)
 $874万
 $28,015/呎
-(21年-07月-26日)</t>
+(21年-07月-27日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -27993,7 +27993,7 @@
           <t>C | 449呎 (2房)
 $1225万
 $27,283/呎
-(24年-12月-22日)</t>
+(24年-12月-23日)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -28001,7 +28001,7 @@
           <t>D | 311呎 (1房)
 $812万
 $26,109/呎
-(25年-06月-29日)</t>
+(25年-06月-30日)</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
@@ -28009,7 +28009,7 @@
           <t>E | 525呎 (2房)
 $1367万
 $26,045/呎
-(24年-10月-29日)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
     </row>
@@ -28024,7 +28024,7 @@
           <t>A | 584呎 (2房)
 $1404万
 $24,033/呎
-(24年-07月-23日)</t>
+(24年-07月-24日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -28032,7 +28032,7 @@
           <t>B | 312呎 (1房)
 $823万
 $26,392/呎
-(21年-06月-29日)</t>
+(21年-06月-30日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -28040,7 +28040,7 @@
           <t>C | 449呎 (2房)
 $1220万
 $27,170/呎
-(24年-04月-08日)</t>
+(24年-04月-09日)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -28048,7 +28048,7 @@
           <t>D | 311呎 (1房)
 $884万
 $28,438/呎
-(21年-08月-29日)</t>
+(21年-08月-30日)</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
@@ -28056,7 +28056,7 @@
           <t>E | 525呎 (2房)
 $1361万
 $25,917/呎
-(24年-05月-03日)</t>
+(24年-05月-04日)</t>
         </is>
       </c>
     </row>
@@ -28071,7 +28071,7 @@
           <t>A | 584呎 (2房)
 $1397万
 $23,913/呎
-(24年-06月-19日)</t>
+(24年-06月-20日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -28079,7 +28079,7 @@
           <t>B | 312呎 (1房)
 $855万
 $27,408/呎
-(21年-07月-01日)</t>
+(21年-07月-02日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -28087,7 +28087,7 @@
           <t>C | 449呎 (2房)
 $1214万
 $27,035/呎
-(24年-03月-27日)</t>
+(24年-03月-28日)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -28095,7 +28095,7 @@
           <t>D | 311呎 (1房)
 $880万
 $28,295/呎
-(21年-08月-19日)</t>
+(21年-08月-20日)</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
@@ -28103,7 +28103,7 @@
           <t>E | 525呎 (2房)
 $1354万
 $25,787/呎
-(24年-04月-28日)</t>
+(24年-04月-29日)</t>
         </is>
       </c>
     </row>
@@ -28118,10 +28118,57 @@
           <t>A | 584呎 (2房)
 $1348万
 $23,081/呎
-(24年-06月-24日)</t>
+(24年-06月-25日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>B | 312呎 (1房)
+$851万
+$27,274/呎
+(21年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>C | 449呎 (2房)
+$1260万
+$28,062/呎
+(21年-11月-21日)</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
+        <is>
+          <t>D | 311呎 (1房)
+$876万
+$28,155/呎
+(21年-07月-22日)</t>
+        </is>
+      </c>
+      <c r="F17" s="20" t="inlineStr">
+        <is>
+          <t>E | 525呎 (2房)
+$1364万
+$25,976/呎
+(25年-04月-03日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>A | 584呎 (2房)
+$1390万
+$23,793/呎
+(24年-07月-17日)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
         <is>
           <t>B | 312呎 (1房)
 $851万
@@ -28129,59 +28176,12 @@
 (21年-07月-06日)</t>
         </is>
       </c>
-      <c r="D17" s="20" t="inlineStr">
-        <is>
-          <t>C | 449呎 (2房)
-$1260万
-$28,062/呎
-(21年-11月-20日)</t>
-        </is>
-      </c>
-      <c r="E17" s="20" t="inlineStr">
-        <is>
-          <t>D | 311呎 (1房)
-$876万
-$28,155/呎
-(21年-07月-21日)</t>
-        </is>
-      </c>
-      <c r="F17" s="20" t="inlineStr">
-        <is>
-          <t>E | 525呎 (2房)
-$1364万
-$25,976/呎
-(25年-04月-02日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="58" customHeight="1">
-      <c r="A18" s="19" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B18" s="20" t="inlineStr">
-        <is>
-          <t>A | 584呎 (2房)
-$1390万
-$23,793/呎
-(24年-07月-16日)</t>
-        </is>
-      </c>
-      <c r="C18" s="20" t="inlineStr">
-        <is>
-          <t>B | 312呎 (1房)
-$851万
-$27,274/呎
-(21年-07月-05日)</t>
-        </is>
-      </c>
       <c r="D18" s="20" t="inlineStr">
         <is>
           <t>C | 449呎 (2房)
 $1208万
 $26,900/呎
-(23年-06月-11日)</t>
+(23年-06月-12日)</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -28189,7 +28189,7 @@
           <t>D | 311呎 (1房)
 $892万
 $28,676/呎
-(21年-07月-28日)</t>
+(21年-07月-29日)</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -28197,7 +28197,7 @@
           <t>E | 525呎 (2房)
 $1347万
 $25,659/呎
-(25年-10月-16日)</t>
+(25年-10月-17日)</t>
         </is>
       </c>
     </row>
@@ -28212,7 +28212,7 @@
           <t>A | 584呎 (2房)
 $1376万
 $23,557/呎
-(24年-06月-03日)</t>
+(24年-06月-04日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -28220,7 +28220,7 @@
           <t>B | 312呎 (1房)
 $822万
 $26,357/呎
-(21年-07月-05日)</t>
+(21年-07月-06日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -28228,7 +28228,7 @@
           <t>C | 449呎 (2房)
 $1248万
 $27,785/呎
-(21年-11月-29日)</t>
+(21年-11月-30日)</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -28236,7 +28236,7 @@
           <t>D | 311呎 (1房)
 $904万
 $29,080/呎
-(21年-07月-19日)</t>
+(21年-07月-20日)</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
@@ -28244,7 +28244,7 @@
           <t>E | 525呎 (2房)
 $1334万
 $25,405/呎
-(24年-05月-20日)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
     </row>
@@ -28259,7 +28259,7 @@
           <t>A | 584呎 (2房)
 $1369万
 $23,441/呎
-(24年-06月-03日)</t>
+(24年-06月-04日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -28267,7 +28267,7 @@
           <t>B | 312呎 (1房)
 $838万
 $26,870/呎
-(21年-04月-21日)</t>
+(21年-04月-22日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -28275,7 +28275,7 @@
           <t>C | 449呎 (2房)
 $1190万
 $26,503/呎
-(21年-09月-28日)</t>
+(21年-09月-29日)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -28283,7 +28283,7 @@
           <t>D | 311呎 (1房)
 $900万
 $28,936/呎
-(21年-07月-13日)</t>
+(21年-07月-14日)</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -28291,7 +28291,7 @@
           <t>E | 525呎 (2房)
 $1327万
 $25,278/呎
-(24年-06月-05日)</t>
+(24年-06月-06日)</t>
         </is>
       </c>
     </row>
@@ -28306,7 +28306,7 @@
           <t>A | 584呎 (2房)
 $1362万
 $23,324/呎
-(24年-05月-30日)</t>
+(24年-05月-31日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -28314,7 +28314,7 @@
           <t>B | 312呎 (1房)
 $799万
 $25,615/呎
-(21年-05月-13日)</t>
+(21年-05月-14日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -28322,7 +28322,7 @@
           <t>C | 449呎 (2房)
 $1213万
 $27,022/呎
-(21年-10月-22日)</t>
+(21年-10月-23日)</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
@@ -28330,7 +28330,7 @@
           <t>D | 311呎 (1房)
 $805万
 $25,894/呎
-(25年-06月-23日)</t>
+(25年-06月-24日)</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -28338,7 +28338,7 @@
           <t>E | 525呎 (2房)
 $1321万
 $25,153/呎
-(24年-05月-01日)</t>
+(24年-05月-02日)</t>
         </is>
       </c>
     </row>
@@ -28353,7 +28353,7 @@
           <t>A | 584呎 (2房)
 $1355万
 $23,210/呎
-(24年-06月-10日)</t>
+(24年-06月-11日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -28361,7 +28361,7 @@
           <t>B | 312呎 (1房)
 $830万
 $26,602/呎
-(21年-05月-23日)</t>
+(21年-05月-24日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -28369,7 +28369,7 @@
           <t>C | 449呎 (2房)
 $1229万
 $27,373/呎
-(21年-06月-30日)</t>
+(21年-07月-01日)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -28377,7 +28377,7 @@
           <t>D | 311呎 (1房)
 $801万
 $25,767/呎
-(25年-06月-23日)</t>
+(25年-06月-24日)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
@@ -28385,7 +28385,7 @@
           <t>E | 525呎 (2房)
 $1314万
 $25,027/呎
-(24年-04月-22日)</t>
+(24年-04月-23日)</t>
         </is>
       </c>
     </row>
@@ -28400,7 +28400,7 @@
           <t>A | 584呎 (2房)
 $1349万
 $23,092/呎
-(24年-06月-06日)</t>
+(24年-06月-07日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -28408,7 +28408,7 @@
           <t>B | 312呎 (1房)
 $791万
 $25,359/呎
-(21年-05月-02日)</t>
+(21年-05月-03日)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -28416,7 +28416,7 @@
           <t>C | 449呎 (2房)
 $1172万
 $26,109/呎
-(24年-06月-26日)</t>
+(24年-06月-27日)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
@@ -28424,7 +28424,7 @@
           <t>D | 311呎 (1房)
 $886万
 $28,504/呎
-(21年-07月-14日)</t>
+(21年-07月-15日)</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -28432,7 +28432,7 @@
           <t>E | 525呎 (2房)
 $1307万
 $24,903/呎
-(24年-04月-22日)</t>
+(24年-04月-23日)</t>
         </is>
       </c>
     </row>
@@ -28447,7 +28447,7 @@
           <t>A | 584呎 (2房)
 $1302万
 $22,290/呎
-(24年-09月-10日)</t>
+(24年-09月-11日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -28455,7 +28455,7 @@
           <t>B | 312呎 (1房)
 $787万
 $25,233/呎
-(21年-05月-24日)</t>
+(21年-05月-25日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -28463,7 +28463,7 @@
           <t>C | 449呎 (2房)
 $1217万
 $27,100/呎
-(21年-07月-27日)</t>
+(21年-07月-28日)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -28471,7 +28471,7 @@
           <t>D | 311呎 (1房)
 $882万
 $28,363/呎
-(21年-07月-08日)</t>
+(21年-07月-09日)</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
@@ -28479,7 +28479,7 @@
           <t>E | 525呎 (2房)
 $1301万
 $24,778/呎
-(24年-05月-01日)</t>
+(24年-05月-02日)</t>
         </is>
       </c>
     </row>
@@ -28494,7 +28494,7 @@
           <t>A | 584呎 (2房)
 $1335万
 $22,864/呎
-(24年-06月-06日)</t>
+(24年-06月-07日)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -28502,7 +28502,7 @@
           <t>B | 312呎 (1房)
 $818万
 $26,209/呎
-(21年-06月-02日)</t>
+(21年-06月-03日)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -28510,7 +28510,7 @@
           <t>C | 449呎 (2房)
 $1211万
 $26,967/呎
-(21年-08月-03日)</t>
+(21年-08月-04日)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
@@ -28518,7 +28518,7 @@
           <t>D | 311呎 (1房)
 $867万
 $27,890/呎
-(21年-06月-29日)</t>
+(21年-06月-30日)</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -28526,7 +28526,7 @@
           <t>E | 525呎 (2房)
 $1294万
 $24,655/呎
-(24年-04月-28日)</t>
+(24年-04月-29日)</t>
         </is>
       </c>
     </row>
@@ -28541,7 +28541,7 @@
           <t>A | 584呎 (2房)
 $1295万
 $22,179/呎
-(24年-08月-08日)</t>
+(24年-08月-09日)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -28549,7 +28549,7 @@
           <t>B | 312呎 (1房)
 $783万
 $25,110/呎
-(21年-05月-16日)</t>
+(21年-05月-17日)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -28557,7 +28557,7 @@
           <t>C | 449呎 (2房)
 $1161万
 $25,849/呎
-(24年-11月-19日)</t>
+(24年-11月-20日)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
@@ -28565,7 +28565,7 @@
           <t>D | 311呎 (1房)
 $878万
 $28,224/呎
-(21年-07月-13日)</t>
+(21年-07月-14日)</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
@@ -28573,7 +28573,7 @@
           <t>E | 525呎 (2房)
 $1294万
 $24,655/呎
-(24年-05月-05日)</t>
+(24年-05月-06日)</t>
         </is>
       </c>
     </row>
@@ -28588,7 +28588,7 @@
           <t>A | 584呎 (2房)
 $1282万
 $21,960/呎
-(24年-09月-23日)</t>
+(24年-09月-24日)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -28596,7 +28596,7 @@
           <t>B | 312呎 (1房)
 $790万
 $25,325/呎
-(21年-04月-03日)</t>
+(21年-04月-04日)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -28604,7 +28604,7 @@
           <t>C | 449呎 (2房)
 $1149万
 $25,595/呎
-(21年-07月-24日)</t>
+(21年-07月-25日)</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr">
@@ -28612,7 +28612,7 @@
           <t>D | 311呎 (1房)
 $869万
 $27,945/呎
-(21年-07月-26日)</t>
+(21年-07月-27日)</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
@@ -28620,7 +28620,7 @@
           <t>E | 525呎 (2房)
 $1282万
 $24,413/呎
-(24年-05月-05日)</t>
+(24年-05月-06日)</t>
         </is>
       </c>
     </row>
@@ -28635,7 +28635,7 @@
           <t>A | 584呎 (2房)
 $1276万
 $21,851/呎
-(24年-10月-02日)</t>
+(24年-10月-03日)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -28643,7 +28643,7 @@
           <t>B | 312呎 (1房)
 $806万
 $25,821/呎
-(21年-04月-26日)</t>
+(21年-04月-27日)</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -28651,7 +28651,7 @@
           <t>C | 449呎 (2房)
 $1143万
 $25,465/呎
-(24年-05月-23日)</t>
+(24年-05月-24日)</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
@@ -28659,7 +28659,7 @@
           <t>D | 311呎 (1房)
 $865万
 $27,806/呎
-(21年-07月-25日)</t>
+(21年-07月-26日)</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
@@ -28667,7 +28667,7 @@
           <t>E | 525呎 (2房)
 $1291万
 $24,590/呎
-(24年-05月-02日)</t>
+(24年-05月-03日)</t>
         </is>
       </c>
     </row>
@@ -28682,7 +28682,7 @@
           <t>A | 584呎 (2房)
 $1274万
 $21,808/呎
-(24年-10月-07日)</t>
+(24年-10月-08日)</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
@@ -28690,7 +28690,7 @@
           <t>B | 312呎 (1房)
 $804万
 $25,767/呎
-(21年-06月-29日)</t>
+(21年-06月-30日)</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
@@ -28698,7 +28698,7 @@
           <t>C | 449呎 (2房)
 $1169万
 $26,044/呎
-(21年-08月-31日)</t>
+(21年-09月-01日)</t>
         </is>
       </c>
       <c r="E29" s="20" t="inlineStr">
@@ -28706,7 +28706,7 @@
           <t>D | 311呎 (1房)
 $863万
 $27,749/呎
-(21年-07月-18日)</t>
+(21年-07月-19日)</t>
         </is>
       </c>
       <c r="F29" s="20" t="inlineStr">
@@ -28714,7 +28714,7 @@
           <t>E | 525呎 (2房)
 $1273万
 $24,243/呎
-(24年-05月-20日)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
     </row>
@@ -28729,7 +28729,7 @@
           <t>A | 584呎 (2房)
 $1271万
 $21,763/呎
-(24年-10月-08日)</t>
+(24年-10月-09日)</t>
         </is>
       </c>
       <c r="C30" s="20" t="inlineStr">
@@ -28737,7 +28737,7 @@
           <t>B | 312呎 (1房)
 $759万
 $24,330/呎
-(25年-07月-01日)</t>
+(25年-07月-02日)</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
@@ -28745,7 +28745,7 @@
           <t>C | 449呎 (2房)
 $1139万
 $25,364/呎
-(24年-05月-07日)</t>
+(24年-05月-08日)</t>
         </is>
       </c>
       <c r="E30" s="20" t="inlineStr">
@@ -28753,7 +28753,7 @@
           <t>D | 311呎 (1房)
 $861万
 $27,695/呎
-(21年-07月-28日)</t>
+(21年-07月-29日)</t>
         </is>
       </c>
       <c r="F30" s="20" t="inlineStr">
@@ -28761,7 +28761,7 @@
           <t>E | 525呎 (2房)
 $1270万
 $24,194/呎
-(24年-05月-07日)</t>
+(24年-05月-08日)</t>
         </is>
       </c>
     </row>
@@ -28776,7 +28776,7 @@
           <t>A | 584呎 (2房)
 $1268万
 $21,720/呎
-(24年-10月-17日)</t>
+(24年-10月-18日)</t>
         </is>
       </c>
       <c r="C31" s="20" t="inlineStr">
@@ -28784,7 +28784,7 @@
           <t>B | 312呎 (1房)
 $777万
 $24,897/呎
-(21年-07月-14日)</t>
+(21年-07月-15日)</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">
@@ -28792,7 +28792,7 @@
           <t>C | 449呎 (2房)
 $1136万
 $25,308/呎
-(23年-06月-15日)</t>
+(23年-06月-16日)</t>
         </is>
       </c>
       <c r="E31" s="20" t="inlineStr">
@@ -28800,7 +28800,7 @@
           <t>D | 311呎 (1房)
 $860万
 $27,640/呎
-(21年-08月-02日)</t>
+(21年-08月-03日)</t>
         </is>
       </c>
       <c r="F31" s="20" t="inlineStr">
@@ -28808,7 +28808,7 @@
           <t>E | 525呎 (2房)
 $1268万
 $24,146/呎
-(24年-11月-27日)</t>
+(24年-11月-28日)</t>
         </is>
       </c>
     </row>
@@ -28823,7 +28823,7 @@
           <t>A | 547呎 (2房)
 $1350万
 $24,680/呎
-(24年-10月-23日)</t>
+(24年-10月-24日)</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
@@ -28831,7 +28831,7 @@
           <t>B | 291呎 (1房)
 $808万
 $27,766/呎
-(24年-04月-15日)</t>
+(24年-04月-16日)</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">
@@ -28839,7 +28839,7 @@
           <t>C | 411呎 (2房)
 $1200万
 $29,197/呎
-(24年-04月-04日)</t>
+(24年-04月-05日)</t>
         </is>
       </c>
       <c r="E32" s="20" t="inlineStr">
@@ -28847,7 +28847,7 @@
           <t>D | 290呎 (1房)
 $865万
 $29,828/呎
-(24年-12月-02日)</t>
+(24年-12月-03日)</t>
         </is>
       </c>
       <c r="F32" s="20" t="inlineStr">
@@ -28855,7 +28855,7 @@
           <t>E | 488呎 (2房)
 $1468万
 $30,082/呎
-(24年-07月-01日)</t>
+(24年-07月-02日)</t>
         </is>
       </c>
     </row>

--- a/web/files/九龙-西南九龙-维港汇 III.xlsx
+++ b/web/files/九龙-西南九龙-维港汇 III.xlsx
@@ -14211,7 +14211,7 @@
         </is>
       </c>
       <c r="E220" s="4" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F220" s="3" t="inlineStr">
         <is>
@@ -14227,7 +14227,7 @@
         <v>8534500</v>
       </c>
       <c r="I220" s="5" t="n">
-        <v>26923</v>
+        <v>26838</v>
       </c>
       <c r="J220" s="3" t="inlineStr">
         <is>
@@ -14238,7 +14238,7 @@
         <v>8534500</v>
       </c>
       <c r="L220" s="5" t="n">
-        <v>26923</v>
+        <v>26838</v>
       </c>
       <c r="M220" s="3" t="inlineStr">
         <is>
@@ -27123,9 +27123,9 @@
       </c>
       <c r="D28" s="20" t="inlineStr">
         <is>
-          <t>C | 317呎 (1房)
+          <t>C | 318呎 (1房)
 $853万
-$26,923/呎
+$26,838/呎
 (21年-04月-21日)</t>
         </is>
       </c>

--- a/web/files/九龙-西南九龙-维港汇 III.xlsx
+++ b/web/files/九龙-西南九龙-维港汇 III.xlsx
@@ -17258,7 +17258,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="H269" s="5" t="n">
@@ -27703,7 +27703,7 @@
           <t>B | 312呎 (1房)
 $789万
 $25,281/呎
-(25年-06月-02日)</t>
+(25年-08月-28日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
